--- a/stories/arbres/TREE-COL-014.xlsx
+++ b/stories/arbres/TREE-COL-014.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Noé est avec maman, au parc. Noé a envie de jouer. maman est là, tout près. On va apprendre : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé écoute maman. Noé entend les mots : écouter, si malaise raconter à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1538,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Noé va vers le bac à sable. Ça sent le pain chaud. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Noé se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On se tait une seconde. maman dit : je suis là. On reste ensemble.</t>
+          <t>Noé va vers le bac à sable. Ça sent le pain chaud. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Noé se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On se tait une seconde. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1676,12 @@
         <v>12</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Noé va vers le bac à sable. Ça sent le pain chaud. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Noé se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On se tait une seconde.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1862,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
         </is>
       </c>
     </row>
@@ -1997,6 +2035,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé respire. Noé retient : écouter, si malaise raconter à la maison. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2183,6 +2226,11 @@
         <v>12</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2345,6 +2393,11 @@
         <v>12</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi le ballon. Le sol est un peu froid. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé répète tout bas : écouter, si malaise raconter à la maison. On dit merci. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2533,6 +2586,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -2697,6 +2755,11 @@
         <v>12</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Tom. Un vélo passe au loin. On se tait une seconde. Cette fin-là est celle de le bac à sable, le ballon et Tom. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2859,6 +2922,11 @@
         <v>12</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3021,6 +3089,11 @@
         <v>12</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Léa. La lumière est claire. On se tient la main. Cette fin-là est celle de le bac à sable, le ballon et Léa. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3183,6 +3256,11 @@
         <v>12</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3345,6 +3423,11 @@
         <v>12</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Sami. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de le bac à sable, le ballon et Sami. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3507,6 +3590,11 @@
         <v>12</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3669,6 +3757,11 @@
         <v>12</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi le seau. Une feuille tombe. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé répète tout bas : écouter, si malaise raconter à la maison. On souffle doucement. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3857,6 +3950,11 @@
       <c r="AV17" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -4021,6 +4119,11 @@
         <v>12</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Tom. La lumière est claire. On se tait une seconde. Cette fin-là est celle de le bac à sable, le seau et Tom. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4183,6 +4286,11 @@
         <v>12</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4345,6 +4453,11 @@
         <v>12</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Léa. Il y a des miettes sur la table. On se tient la main. Cette fin-là est celle de le bac à sable, le seau et Léa. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4507,6 +4620,11 @@
         <v>12</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4669,6 +4787,11 @@
         <v>12</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Sami. Un chat miaule une fois. On range un objet. Cette fin-là est celle de le bac à sable, le seau et Sami. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4831,6 +4954,11 @@
         <v>12</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4993,6 +5121,11 @@
         <v>12</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi le doudou. L'eau coule, tout petit bruit. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé répète tout bas : écouter, si malaise raconter à la maison. On écoute jusqu'au bout. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5181,6 +5314,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -5345,6 +5483,11 @@
         <v>12</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Tom. Il y a des miettes sur la table. On se tait une seconde. Cette fin-là est celle de le bac à sable, le doudou et Tom. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5507,6 +5650,11 @@
         <v>12</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5669,6 +5817,11 @@
         <v>12</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Léa. Un chat miaule une fois. On se tient la main. Cette fin-là est celle de le bac à sable, le doudou et Léa. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5831,6 +5984,11 @@
         <v>12</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5993,6 +6151,11 @@
         <v>12</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Sami. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de le bac à sable, le doudou et Sami. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6155,6 +6318,11 @@
         <v>12</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6179,7 +6347,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Noé va vers le toboggan. Le vent est doux. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Noé se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On se tient la main. maman dit : je suis là. On reste ensemble.</t>
+          <t>Noé va vers le toboggan. Le vent est doux. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Noé se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On se tient la main. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6317,6 +6485,12 @@
         <v>12</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Noé va vers le toboggan. Le vent est doux. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Noé se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On se tient la main.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6497,6 +6671,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
         </is>
       </c>
     </row>
@@ -6665,6 +6844,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé respire. Noé retient : écouter, si malaise raconter à la maison. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6851,6 +7035,11 @@
         <v>12</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7013,6 +7202,11 @@
         <v>12</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi le ballon. Un vélo passe au loin. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé répète tout bas : écouter, si malaise raconter à la maison. On dit merci. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7201,6 +7395,11 @@
       <c r="AV37" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -7365,6 +7564,11 @@
         <v>12</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Tom. La lumière est claire. On se tient la main. Cette fin-là est celle de le toboggan, le ballon et Tom. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7527,6 +7731,11 @@
         <v>12</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7689,6 +7898,11 @@
         <v>12</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Léa. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de le toboggan, le ballon et Léa. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7851,6 +8065,11 @@
         <v>12</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8013,6 +8232,11 @@
         <v>12</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Sami. Un chat miaule une fois. On dit merci. Cette fin-là est celle de le toboggan, le ballon et Sami. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8175,6 +8399,11 @@
         <v>12</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8337,6 +8566,11 @@
         <v>12</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi le seau. La lumière est claire. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé répète tout bas : écouter, si malaise raconter à la maison. On souffle doucement. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8525,6 +8759,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -8689,6 +8928,11 @@
         <v>12</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Tom. Il y a des miettes sur la table. On se tient la main. Cette fin-là est celle de le toboggan, le seau et Tom. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8851,6 +9095,11 @@
         <v>12</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9013,6 +9262,11 @@
         <v>12</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Léa. Un chat miaule une fois. On range un objet. Cette fin-là est celle de le toboggan, le seau et Léa. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9175,6 +9429,11 @@
         <v>12</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9337,6 +9596,11 @@
         <v>12</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Sami. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de le toboggan, le seau et Sami. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9499,6 +9763,11 @@
         <v>12</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9661,6 +9930,11 @@
         <v>12</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi le doudou. Il y a des miettes sur la table. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé répète tout bas : écouter, si malaise raconter à la maison. On écoute jusqu'au bout. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9849,6 +10123,11 @@
       <c r="AV53" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -10013,6 +10292,11 @@
         <v>12</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Tom. Un chat miaule une fois. On se tient la main. Cette fin-là est celle de le toboggan, le doudou et Tom. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10175,6 +10459,11 @@
         <v>12</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10337,6 +10626,11 @@
         <v>12</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Léa. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de le toboggan, le doudou et Léa. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10499,6 +10793,11 @@
         <v>12</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10661,6 +10960,11 @@
         <v>12</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Sami. La couverture est douce. On dit merci. Cette fin-là est celle de le toboggan, le doudou et Sami. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10823,6 +11127,11 @@
         <v>12</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10847,7 +11156,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Noé va vers les balançoires. Le sol est un peu froid. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Noé se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On range un objet. maman dit : je suis là. On reste ensemble.</t>
+          <t>Noé va vers les balançoires. Le sol est un peu froid. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Noé se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On range un objet. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10985,6 +11294,12 @@
         <v>12</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Noé va vers les balançoires. Le sol est un peu froid. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Noé se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On range un objet.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11165,6 +11480,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
         </is>
       </c>
     </row>
@@ -11333,6 +11653,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé respire. Noé retient : écouter, si malaise raconter à la maison. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11519,6 +11844,11 @@
         <v>12</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11681,6 +12011,11 @@
         <v>12</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi le ballon. Un chat miaule une fois. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé répète tout bas : écouter, si malaise raconter à la maison. On dit merci. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11869,6 +12204,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -12033,6 +12373,11 @@
         <v>12</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Tom. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de les balançoires, le ballon et Tom. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12195,6 +12540,11 @@
         <v>12</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12357,6 +12707,11 @@
         <v>12</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Léa. Un chat miaule une fois. On dit merci. Cette fin-là est celle de les balançoires, le ballon et Léa. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12519,6 +12874,11 @@
         <v>12</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12681,6 +13041,11 @@
         <v>12</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Sami. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de les balançoires, le ballon et Sami. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12843,6 +13208,11 @@
         <v>12</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13005,6 +13375,11 @@
         <v>12</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi le seau. Les chaussures font toc toc. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé répète tout bas : écouter, si malaise raconter à la maison. On souffle doucement. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13193,6 +13568,11 @@
       <c r="AV73" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -13357,6 +13737,11 @@
         <v>12</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Tom. Un chat miaule une fois. On range un objet. Cette fin-là est celle de les balançoires, le seau et Tom. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13519,6 +13904,11 @@
         <v>12</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13681,6 +14071,11 @@
         <v>12</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Léa. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de les balançoires, le seau et Léa. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13843,6 +14238,11 @@
         <v>12</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14005,6 +14405,11 @@
         <v>12</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Sami. La couverture est douce. On souffle doucement. Cette fin-là est celle de les balançoires, le seau et Sami. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14167,6 +14572,11 @@
         <v>12</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14329,6 +14739,11 @@
         <v>12</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi le doudou. La couverture est douce. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé répète tout bas : écouter, si malaise raconter à la maison. On écoute jusqu'au bout. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14517,6 +14932,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -14681,6 +15101,11 @@
         <v>12</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Tom. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de les balançoires, le doudou et Tom. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14843,6 +15268,11 @@
         <v>12</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15005,6 +15435,11 @@
         <v>12</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Léa. La couverture est douce. On dit merci. Cette fin-là est celle de les balançoires, le doudou et Léa. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15167,6 +15602,11 @@
         <v>12</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15329,6 +15769,11 @@
         <v>12</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Sami. On entend un oiseau. On souffle doucement. Cette fin-là est celle de les balançoires, le doudou et Sami. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15491,6 +15936,11 @@
         <v>12</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15509,7 +15959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15582,6 +16032,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-COL-014.xlsx
+++ b/stories/arbres/TREE-COL-014.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,11 @@
           <t>narrateur|Aujourd'hui, Noé est avec maman, au parc. Noé a envie de jouer. maman est là, tout près. On va apprendre : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé écoute maman. Noé entend les mots : écouter, si malaise raconter à la maison.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1524,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1682,6 +1693,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1869,6 +1881,7 @@
           <t>narrateur|Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2040,6 +2053,7 @@
           <t>narrateur|Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé respire. Noé retient : écouter, si malaise raconter à la maison. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2231,6 +2245,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2398,6 +2413,7 @@
           <t>narrateur|Noé a choisi le ballon. Le sol est un peu froid. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé répète tout bas : écouter, si malaise raconter à la maison. On dit merci. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2593,6 +2609,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2760,6 +2777,7 @@
           <t>narrateur|Noé rejoint Tom. Un vélo passe au loin. On se tait une seconde. Cette fin-là est celle de le bac à sable, le ballon et Tom. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2927,6 +2945,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3094,6 +3113,7 @@
           <t>narrateur|Noé rejoint Léa. La lumière est claire. On se tient la main. Cette fin-là est celle de le bac à sable, le ballon et Léa. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3261,6 +3281,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3428,6 +3449,7 @@
           <t>narrateur|Noé rejoint Sami. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de le bac à sable, le ballon et Sami. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3595,6 +3617,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3762,6 +3785,7 @@
           <t>narrateur|Noé a choisi le seau. Une feuille tombe. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé répète tout bas : écouter, si malaise raconter à la maison. On souffle doucement. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3957,6 +3981,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4124,6 +4149,7 @@
           <t>narrateur|Noé rejoint Tom. La lumière est claire. On se tait une seconde. Cette fin-là est celle de le bac à sable, le seau et Tom. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4291,6 +4317,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4458,6 +4485,7 @@
           <t>narrateur|Noé rejoint Léa. Il y a des miettes sur la table. On se tient la main. Cette fin-là est celle de le bac à sable, le seau et Léa. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4625,6 +4653,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4792,6 +4821,7 @@
           <t>narrateur|Noé rejoint Sami. Un chat miaule une fois. On range un objet. Cette fin-là est celle de le bac à sable, le seau et Sami. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4959,6 +4989,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5126,6 +5157,7 @@
           <t>narrateur|Noé a choisi le doudou. L'eau coule, tout petit bruit. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé répète tout bas : écouter, si malaise raconter à la maison. On écoute jusqu'au bout. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5321,6 +5353,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5488,6 +5521,7 @@
           <t>narrateur|Noé rejoint Tom. Il y a des miettes sur la table. On se tait une seconde. Cette fin-là est celle de le bac à sable, le doudou et Tom. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5655,6 +5689,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5822,6 +5857,7 @@
           <t>narrateur|Noé rejoint Léa. Un chat miaule une fois. On se tient la main. Cette fin-là est celle de le bac à sable, le doudou et Léa. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5989,6 +6025,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6156,6 +6193,7 @@
           <t>narrateur|Noé rejoint Sami. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de le bac à sable, le doudou et Sami. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6323,6 +6361,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6491,6 +6530,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6678,6 +6718,7 @@
           <t>narrateur|Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6849,6 +6890,7 @@
           <t>narrateur|Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé respire. Noé retient : écouter, si malaise raconter à la maison. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7040,6 +7082,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7207,6 +7250,7 @@
           <t>narrateur|Noé a choisi le ballon. Un vélo passe au loin. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé répète tout bas : écouter, si malaise raconter à la maison. On dit merci. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7402,6 +7446,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7569,6 +7614,7 @@
           <t>narrateur|Noé rejoint Tom. La lumière est claire. On se tient la main. Cette fin-là est celle de le toboggan, le ballon et Tom. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7736,6 +7782,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7903,6 +7950,7 @@
           <t>narrateur|Noé rejoint Léa. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de le toboggan, le ballon et Léa. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8070,6 +8118,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8237,6 +8286,7 @@
           <t>narrateur|Noé rejoint Sami. Un chat miaule une fois. On dit merci. Cette fin-là est celle de le toboggan, le ballon et Sami. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8404,6 +8454,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8571,6 +8622,7 @@
           <t>narrateur|Noé a choisi le seau. La lumière est claire. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé répète tout bas : écouter, si malaise raconter à la maison. On souffle doucement. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8766,6 +8818,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8933,6 +8986,7 @@
           <t>narrateur|Noé rejoint Tom. Il y a des miettes sur la table. On se tient la main. Cette fin-là est celle de le toboggan, le seau et Tom. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9100,6 +9154,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9267,6 +9322,7 @@
           <t>narrateur|Noé rejoint Léa. Un chat miaule une fois. On range un objet. Cette fin-là est celle de le toboggan, le seau et Léa. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9434,6 +9490,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9601,6 +9658,7 @@
           <t>narrateur|Noé rejoint Sami. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de le toboggan, le seau et Sami. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9768,6 +9826,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9935,6 +9994,7 @@
           <t>narrateur|Noé a choisi le doudou. Il y a des miettes sur la table. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé répète tout bas : écouter, si malaise raconter à la maison. On écoute jusqu'au bout. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10130,6 +10190,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10297,6 +10358,7 @@
           <t>narrateur|Noé rejoint Tom. Un chat miaule une fois. On se tient la main. Cette fin-là est celle de le toboggan, le doudou et Tom. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10464,6 +10526,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10631,6 +10694,7 @@
           <t>narrateur|Noé rejoint Léa. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de le toboggan, le doudou et Léa. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10798,6 +10862,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10965,6 +11030,7 @@
           <t>narrateur|Noé rejoint Sami. La couverture est douce. On dit merci. Cette fin-là est celle de le toboggan, le doudou et Sami. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11132,6 +11198,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11300,6 +11367,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11487,6 +11555,7 @@
           <t>narrateur|Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11658,6 +11727,7 @@
           <t>narrateur|Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé respire. Noé retient : écouter, si malaise raconter à la maison. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11849,6 +11919,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12016,6 +12087,7 @@
           <t>narrateur|Noé a choisi le ballon. Un chat miaule une fois. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé répète tout bas : écouter, si malaise raconter à la maison. On dit merci. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12211,6 +12283,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12378,6 +12451,7 @@
           <t>narrateur|Noé rejoint Tom. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de les balançoires, le ballon et Tom. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12545,6 +12619,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12712,6 +12787,7 @@
           <t>narrateur|Noé rejoint Léa. Un chat miaule une fois. On dit merci. Cette fin-là est celle de les balançoires, le ballon et Léa. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12879,6 +12955,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13046,6 +13123,7 @@
           <t>narrateur|Noé rejoint Sami. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de les balançoires, le ballon et Sami. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13213,6 +13291,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13380,6 +13459,7 @@
           <t>narrateur|Noé a choisi le seau. Les chaussures font toc toc. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé répète tout bas : écouter, si malaise raconter à la maison. On souffle doucement. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13575,6 +13655,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13742,6 +13823,7 @@
           <t>narrateur|Noé rejoint Tom. Un chat miaule une fois. On range un objet. Cette fin-là est celle de les balançoires, le seau et Tom. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13909,6 +13991,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14076,6 +14159,7 @@
           <t>narrateur|Noé rejoint Léa. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de les balançoires, le seau et Léa. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14243,6 +14327,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14410,6 +14495,7 @@
           <t>narrateur|Noé rejoint Sami. La couverture est douce. On souffle doucement. Cette fin-là est celle de les balançoires, le seau et Sami. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14577,6 +14663,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14744,6 +14831,7 @@
           <t>narrateur|Noé a choisi le doudou. La couverture est douce. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé répète tout bas : écouter, si malaise raconter à la maison. On écoute jusqu'au bout. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14939,6 +15027,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15106,6 +15195,7 @@
           <t>narrateur|Noé rejoint Tom. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de les balançoires, le doudou et Tom. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15273,6 +15363,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15440,6 +15531,7 @@
           <t>narrateur|Noé rejoint Léa. La couverture est douce. On dit merci. Cette fin-là est celle de les balançoires, le doudou et Léa. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15607,6 +15699,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15774,6 +15867,7 @@
           <t>narrateur|Noé rejoint Sami. On entend un oiseau. On souffle doucement. Cette fin-là est celle de les balançoires, le doudou et Sami. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15941,6 +16035,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15959,7 +16054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16039,6 +16134,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16053,7 +16162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16240,6 +16349,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-COL-014.xlsx
+++ b/stories/arbres/TREE-COL-014.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Écouter la maîtresse, en parler à la maison — au parc</t>
+          <t>Le gant rouge de Nina</t>
         </is>
       </c>
     </row>
@@ -843,6 +843,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Une flaque tient le ciel. Le gant rouge de Nina sèche. Elle a écouté la maîtresse. Un chuchotement a serré son ventre. Elle raconte à la maison, au parc.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1197,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Aujourd'hui, Noé est avec maman, au parc. Noé a envie de jouer. maman est là, tout près. On va apprendre : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé écoute maman. Noé entend les mots : écouter, si malaise raconter à la maison.</t>
+          <t>Une flaque tient le ciel. Le ciel est tout petit, tout bleu. Un gant rouge sèche sur la barrière. Le toboggan brille, encore froid. Ça sent le sable mouillé. Le cartable de Nina est contre le banc. Ton gant a trop d'eau, Nina. Il est lourd. Je l'ai posé là. Il va sécher. En ce moment, Nina est au parc. Son manteau sent encore la classe. Elle a écouté la maîtresse. Un camarade a parlé tout bas. Le ventre de Nina s'est serré. J'ai un malaise, maman. Tu as bien fait de le dire. On écoute la maîtresse. Si malaise, on raconte à la maison. Je raconte à la maison. Je t'écoute aussi. Le sable est froid sous les bottes. Le seau est rouge, un peu penché. Tu as écouté, à l'école ? Oui. J'ai écouté. Bravo, Nina. C'est du bon travail. Une feuille colle au toboggan. On reste un moment, ici. D'accord. Une corneille marche près du seau. Ton ventre est un peu moins serré ? Un peu.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1325,12 +1337,44 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Aujourd'hui, Noé est avec maman, au parc. Noé a envie de jouer. maman est là, tout près. On va apprendre : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé écoute maman. Noé entend les mots : écouter, si malaise raconter à la maison.</t>
+          <t>narrateur|Une flaque tient le ciel.
+narrateur|Le ciel est tout petit, tout bleu.
+narrateur|Un gant rouge sèche sur la barrière.
+narrateur|Le toboggan brille, encore froid.
+narrateur|Ça sent le sable mouillé.
+narrateur|Le cartable de Nina est contre le banc.
+maman|Ton gant a trop d'eau, Nina.
+enfant-f|Il est lourd.
+papa|Je l'ai posé là.
+papa|Il va sécher.
+narrateur|En ce moment, Nina est au parc.
+narrateur|Son manteau sent encore la classe.
+narrateur|Elle a écouté la maîtresse.
+narrateur|Un camarade a parlé tout bas.
+narrateur|Le ventre de Nina s'est serré.
+enfant-f|J'ai un malaise, maman.
+maman|Tu as bien fait de le dire.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+enfant-f|Je raconte à la maison.
+papa|Je t'écoute aussi.
+narrateur|Le sable est froid sous les bottes.
+narrateur|Le seau est rouge, un peu penché.
+maman|Tu as écouté, à l'école ?
+enfant-f|Oui. J'ai écouté.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+narrateur|Une feuille colle au toboggan.
+maman|On reste un moment, ici.
+enfant-f|D'accord.
+narrateur|Une corneille marche près du seau.
+papa|Ton ventre est un peu moins serré ?
+enfant-f|Un peu.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>enfants_parc</t>
+          <t>enfants_parc,flaque</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1401,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+          <t>Nina va où, dans le parc ? Le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1521,7 +1565,8 @@
       <c r="AV3" s="2" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+          <t>narrateur|Nina va où, dans le parc ?
+maman|Le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1549,7 +1594,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Noé va vers le bac à sable. Ça sent le pain chaud. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Noé se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On se tait une seconde. Je suis là. On reste ensemble.</t>
+          <t>Nina va vers le bac à sable. Le sable est froid, un peu lourd. Une petite pelle brille, toute mouillée. Elle se souvient de la classe. Elle a écouté la maîtresse. Le camarade a parlé d'un secret, tout bas. Mon ventre est serré. C'est un malaise. Ce soir, tu racontes à la maison. Je raconte à papa et maman. Oui. On écoute la maîtresse. Si malaise, on raconte à la maison. Je t'écoute, déjà. Nina pose une main dans le sable. Bravo, Nina. Tu as parlé. Le gant rouge sèche, plus loin.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1689,11 +1734,29 @@
       <c r="AV4" s="2" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Noé va vers le bac à sable. Ça sent le pain chaud. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Noé se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On se tait une seconde.
-maman|Je suis là. On reste ensemble.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Nina va vers le bac à sable.
+narrateur|Le sable est froid, un peu lourd.
+narrateur|Une petite pelle brille, toute mouillée.
+narrateur|Elle se souvient de la classe.
+narrateur|Elle a écouté la maîtresse.
+narrateur|Le camarade a parlé d'un secret, tout bas.
+enfant-f|Mon ventre est serré.
+maman|C'est un malaise.
+maman|Ce soir, tu racontes à la maison.
+enfant-f|Je raconte à papa et maman.
+maman|Oui. On écoute la maîtresse.
+papa|Si malaise, on raconte à la maison.
+papa|Je t'écoute, déjà.
+narrateur|Nina pose une main dans le sable.
+maman|Bravo, Nina. Tu as parlé.
+narrateur|Le gant rouge sèche, plus loin.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>sable</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1718,7 +1781,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
+          <t>On écoute la maîtresse ? Si malaise, on raconte à la maison ?</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1878,7 +1941,8 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
+          <t>narrateur|On écoute la maîtresse ?
+maman|Si malaise, on raconte à la maison ?</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1906,7 +1970,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé respire. Noé retient : écouter, si malaise raconter à la maison. On continue, avec maman.</t>
+          <t>Oui. On écoute la maîtresse. Si malaise, raconter à la maison. Nina respire, tout calme. Bravo, Nina. Tu as fait du bon travail. Je raconte à la maison.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2050,7 +2114,13 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé respire. Noé retient : écouter, si malaise raconter à la maison. On continue, avec maman.</t>
+          <t>narrateur|Oui.
+maman|On écoute la maîtresse.
+maman|Si malaise, raconter à la maison.
+narrateur|Nina respire, tout calme.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+enfant-f|Je raconte à la maison.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2078,7 +2148,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>Nina prend quoi ? Le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -2242,7 +2312,8 @@
       <c r="AV7" s="2" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>narrateur|Nina prend quoi ?
+papa|Le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr"/>
@@ -2270,7 +2341,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Noé a choisi le ballon. Le sol est un peu froid. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé répète tout bas : écouter, si malaise raconter à la maison. On dit merci. papa n'est pas loin.</t>
+          <t>Plus tard, Nina prend le ballon. Le ballon a un peu de sable. Elle est encore au bac à sable. J'ai écouté la maîtresse. J'ai un malaise. Tu as bien fait de raconter. Tu as écouté, à l'école. Si malaise, tu viens nous le dire. Je raconte à la maison. Bravo, Nina. C'est du bon travail. Le ballon est un peu froid. Je t'écoute. On reste un moment.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2410,10 +2481,26 @@
       <c r="AV8" s="2" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>narrateur|Noé a choisi le ballon. Le sol est un peu froid. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé répète tout bas : écouter, si malaise raconter à la maison. On dit merci. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr"/>
+          <t>narrateur|Plus tard, Nina prend le ballon.
+narrateur|Le ballon a un peu de sable.
+narrateur|Elle est encore au bac à sable.
+enfant-f|J'ai écouté la maîtresse.
+enfant-f|J'ai un malaise.
+papa|Tu as bien fait de raconter.
+maman|Tu as écouté, à l'école.
+papa|Si malaise, tu viens nous le dire.
+enfant-f|Je raconte à la maison.
+maman|Bravo, Nina.
+maman|C'est du bon travail.
+narrateur|Le ballon est un peu froid.
+papa|Je t'écoute. On reste un moment.</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>ballon</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2438,7 +2525,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Qui arrive, au parc ? Nino, Mila, ou Raphaël.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2606,7 +2693,8 @@
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Qui arrive, au parc ?
+maman|Nino, Mila, ou Raphaël.</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr"/>
@@ -2634,7 +2722,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint Tom. Un vélo passe au loin. On se tait une seconde. Cette fin-là est celle de le bac à sable, le ballon et Tom. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
+          <t>Nino arrive, les genoux sablés. Il a une feuille collée au pantalon. Nina tient le ballon contre son manteau. Nina est au bac à sable. Elle a le ballon. Bonjour, Nino. Bonjour, Nina. J'ai raconté mon malaise. Oui. Tu as écouté, puis raconté. Si malaise, raconter à la maison. Tu as parlé à maman ? Oui. Et à papa. On écoute la maîtresse. Puis on raconte, à la maison. Le ventre de Nina se desserre, tout doucement. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2774,10 +2862,29 @@
       <c r="AV10" s="2" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>narrateur|Noé rejoint Tom. Un vélo passe au loin. On se tait une seconde. Cette fin-là est celle de le bac à sable, le ballon et Tom. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr"/>
+          <t>narrateur|Nino arrive, les genoux sablés.
+narrateur|Il a une feuille collée au pantalon.
+narrateur|Nina tient le ballon contre son manteau.
+narrateur|Nina est au bac à sable.
+narrateur|Elle a le ballon.
+enfant-f|Bonjour, Nino.
+enfant-m|Bonjour, Nina.
+enfant-f|J'ai raconté mon malaise.
+papa|Oui. Tu as écouté, puis raconté.
+maman|Si malaise, raconter à la maison.
+enfant-m|Tu as parlé à maman ?
+enfant-f|Oui. Et à papa.
+papa|On écoute la maîtresse.
+maman|Puis on raconte, à la maison.
+narrateur|Le ventre de Nina se desserre, tout doucement.
+enfant-f|Merci, papa. Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2802,7 +2909,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué au bac à sable. Elle a pris le ballon. Nino est venu. Le sable est resté froid, tout calme. J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. On t'a écoutée. Si malaise, tu reviens nous le dire. Le gant rouge est presque sec. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2942,7 +3049,17 @@
       <c r="AV11" s="2" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a joué au bac à sable.
+narrateur|Elle a pris le ballon.
+narrateur|Nino est venu.
+narrateur|Le sable est resté froid, tout calme.
+enfant-f|J'ai écouté. Puis j'ai raconté.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+maman|On t'a écoutée.
+maman|Si malaise, tu reviens nous le dire.
+narrateur|Le gant rouge est presque sec.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr"/>
@@ -2970,7 +3087,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint Léa. La lumière est claire. On se tient la main. Cette fin-là est celle de le bac à sable, le ballon et Léa. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
+          <t>Mila arrive, un bonnet bleu. Une mèche est encore mouillée. Nina fait rouler le ballon, tout doux. Nina est au bac à sable. Elle a le ballon. Bonjour, Mila. Bonjour, Nina. J'ai raconté mon malaise. Oui. Tu as écouté, puis raconté. Si malaise, raconter à la maison. Tu as parlé à maman ? Oui. Et à papa. On écoute la maîtresse. Puis on raconte, à la maison. Le ventre de Nina se desserre, tout doucement. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3110,10 +3227,29 @@
       <c r="AV12" s="2" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>narrateur|Noé rejoint Léa. La lumière est claire. On se tient la main. Cette fin-là est celle de le bac à sable, le ballon et Léa. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr"/>
+          <t>narrateur|Mila arrive, un bonnet bleu.
+narrateur|Une mèche est encore mouillée.
+narrateur|Nina fait rouler le ballon, tout doux.
+narrateur|Nina est au bac à sable.
+narrateur|Elle a le ballon.
+enfant-f|Bonjour, Mila.
+enfant-f|Bonjour, Nina.
+enfant-f|J'ai raconté mon malaise.
+papa|Oui. Tu as écouté, puis raconté.
+maman|Si malaise, raconter à la maison.
+enfant-f|Tu as parlé à maman ?
+enfant-f|Oui. Et à papa.
+papa|On écoute la maîtresse.
+maman|Puis on raconte, à la maison.
+narrateur|Le ventre de Nina se desserre, tout doucement.
+enfant-f|Merci, papa. Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3138,7 +3274,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué au bac à sable. Elle a pris le ballon. Mila est venue. Le sable est resté froid, tout calme. J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. On t'a écoutée. Si malaise, tu reviens nous le dire. Le gant rouge est presque sec. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3278,7 +3414,17 @@
       <c r="AV13" s="2" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a joué au bac à sable.
+narrateur|Elle a pris le ballon.
+narrateur|Mila est venue.
+narrateur|Le sable est resté froid, tout calme.
+enfant-f|J'ai écouté. Puis j'ai raconté.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+maman|On t'a écoutée.
+maman|Si malaise, tu reviens nous le dire.
+narrateur|Le gant rouge est presque sec.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr"/>
@@ -3306,7 +3452,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint Sami. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de le bac à sable, le ballon et Sami. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
+          <t>Raphaël arrive, les bottes rouges. Il a un bâton de bois, trop grand. Nina pose le ballon près du bac. Nina est au bac à sable. Elle a le ballon. Bonjour, Raphaël. Bonjour, Nina. J'ai raconté mon malaise. Oui. Tu as écouté, puis raconté. Si malaise, raconter à la maison. Tu as parlé à maman ? Oui. Et à papa. On écoute la maîtresse. Puis on raconte, à la maison. Le ventre de Nina se desserre, tout doucement. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3446,10 +3592,29 @@
       <c r="AV14" s="2" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>narrateur|Noé rejoint Sami. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de le bac à sable, le ballon et Sami. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr"/>
+          <t>narrateur|Raphaël arrive, les bottes rouges.
+narrateur|Il a un bâton de bois, trop grand.
+narrateur|Nina pose le ballon près du bac.
+narrateur|Nina est au bac à sable.
+narrateur|Elle a le ballon.
+enfant-f|Bonjour, Raphaël.
+enfant-m|Bonjour, Nina.
+enfant-f|J'ai raconté mon malaise.
+papa|Oui. Tu as écouté, puis raconté.
+maman|Si malaise, raconter à la maison.
+enfant-m|Tu as parlé à maman ?
+enfant-f|Oui. Et à papa.
+papa|On écoute la maîtresse.
+maman|Puis on raconte, à la maison.
+narrateur|Le ventre de Nina se desserre, tout doucement.
+enfant-f|Merci, papa. Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3474,7 +3639,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué au bac à sable. Elle a pris le ballon. Raphaël est venu. Le sable est resté froid, tout calme. J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. On t'a écoutée. Si malaise, tu reviens nous le dire. Le gant rouge est presque sec. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3614,7 +3779,17 @@
       <c r="AV15" s="2" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a joué au bac à sable.
+narrateur|Elle a pris le ballon.
+narrateur|Raphaël est venu.
+narrateur|Le sable est resté froid, tout calme.
+enfant-f|J'ai écouté. Puis j'ai raconté.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+maman|On t'a écoutée.
+maman|Si malaise, tu reviens nous le dire.
+narrateur|Le gant rouge est presque sec.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr"/>
@@ -3642,7 +3817,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Noé a choisi le seau. Une feuille tombe. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé répète tout bas : écouter, si malaise raconter à la maison. On souffle doucement. papa n'est pas loin.</t>
+          <t>Plus tard, Nina prend le seau. Le seau est plein de sable mouillé. Elle pense encore au bac à sable. J'ai écouté la maîtresse. J'ai eu un malaise. Raconte. On est là. Un camarade a parlé tout bas. Tu as bien fait de le dire. À la maison. On écoute la maîtresse. Si malaise, raconter à papa ou maman. Bravo. Ton ventre peut se desserrer. Une goutte glisse du bord du seau. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3782,10 +3957,27 @@
       <c r="AV16" s="2" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>narrateur|Noé a choisi le seau. Une feuille tombe. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé répète tout bas : écouter, si malaise raconter à la maison. On souffle doucement. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr"/>
+          <t>narrateur|Plus tard, Nina prend le seau.
+narrateur|Le seau est plein de sable mouillé.
+narrateur|Elle pense encore au bac à sable.
+enfant-f|J'ai écouté la maîtresse.
+enfant-f|J'ai eu un malaise.
+papa|Raconte. On est là.
+enfant-f|Un camarade a parlé tout bas.
+maman|Tu as bien fait de le dire.
+maman|À la maison.
+papa|On écoute la maîtresse.
+papa|Si malaise, raconter à papa ou maman.
+maman|Bravo. Ton ventre peut se desserrer.
+narrateur|Une goutte glisse du bord du seau.
+enfant-f|Merci, papa. Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>seau</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3810,7 +4002,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Qui arrive, au parc ? Nino, Mila, ou Raphaël.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -3978,7 +4170,8 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Qui arrive, au parc ?
+maman|Nino, Mila, ou Raphaël.</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr"/>
@@ -4006,7 +4199,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint Tom. La lumière est claire. On se tait une seconde. Cette fin-là est celle de le bac à sable, le seau et Tom. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
+          <t>Nino s'accroupit près du seau. Le sable fait un petit tas. Nina reverse une pelletée. Nina est au bac à sable. Elle a le seau. Bonjour, Nino. Bonjour, Nina. J'ai raconté mon malaise. Oui. Tu as écouté, puis raconté. Si malaise, raconter à la maison. Tu as parlé à maman ? Oui. Et à papa. On écoute la maîtresse. Puis on raconte, à la maison. Le ventre de Nina se desserre, tout doucement. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4146,10 +4339,29 @@
       <c r="AV18" s="2" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>narrateur|Noé rejoint Tom. La lumière est claire. On se tait une seconde. Cette fin-là est celle de le bac à sable, le seau et Tom. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr"/>
+          <t>narrateur|Nino s'accroupit près du seau.
+narrateur|Le sable fait un petit tas.
+narrateur|Nina reverse une pelletée.
+narrateur|Nina est au bac à sable.
+narrateur|Elle a le seau.
+enfant-f|Bonjour, Nino.
+enfant-m|Bonjour, Nina.
+enfant-f|J'ai raconté mon malaise.
+papa|Oui. Tu as écouté, puis raconté.
+maman|Si malaise, raconter à la maison.
+enfant-m|Tu as parlé à maman ?
+enfant-f|Oui. Et à papa.
+papa|On écoute la maîtresse.
+maman|Puis on raconte, à la maison.
+narrateur|Le ventre de Nina se desserre, tout doucement.
+enfant-f|Merci, papa. Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4174,7 +4386,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué au bac à sable. Elle a pris le seau. Nino est venu. Le sable est resté froid, tout calme. J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. On t'a écoutée. Si malaise, tu reviens nous le dire. Le gant rouge est presque sec. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4314,7 +4526,17 @@
       <c r="AV19" s="2" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a joué au bac à sable.
+narrateur|Elle a pris le seau.
+narrateur|Nino est venu.
+narrateur|Le sable est resté froid, tout calme.
+enfant-f|J'ai écouté. Puis j'ai raconté.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+maman|On t'a écoutée.
+maman|Si malaise, tu reviens nous le dire.
+narrateur|Le gant rouge est presque sec.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr"/>
@@ -4342,7 +4564,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint Léa. Il y a des miettes sur la table. On se tient la main. Cette fin-là est celle de le bac à sable, le seau et Léa. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
+          <t>Mila touche le bord du seau. Le plastique est froid, un peu rêche. Nina sourit, tout petit. Nina est au bac à sable. Elle a le seau. Bonjour, Mila. Bonjour, Nina. J'ai raconté mon malaise. Oui. Tu as écouté, puis raconté. Si malaise, raconter à la maison. Tu as parlé à maman ? Oui. Et à papa. On écoute la maîtresse. Puis on raconte, à la maison. Le ventre de Nina se desserre, tout doucement. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4482,10 +4704,29 @@
       <c r="AV20" s="2" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>narrateur|Noé rejoint Léa. Il y a des miettes sur la table. On se tient la main. Cette fin-là est celle de le bac à sable, le seau et Léa. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr"/>
+          <t>narrateur|Mila touche le bord du seau.
+narrateur|Le plastique est froid, un peu rêche.
+narrateur|Nina sourit, tout petit.
+narrateur|Nina est au bac à sable.
+narrateur|Elle a le seau.
+enfant-f|Bonjour, Mila.
+enfant-f|Bonjour, Nina.
+enfant-f|J'ai raconté mon malaise.
+papa|Oui. Tu as écouté, puis raconté.
+maman|Si malaise, raconter à la maison.
+enfant-f|Tu as parlé à maman ?
+enfant-f|Oui. Et à papa.
+papa|On écoute la maîtresse.
+maman|Puis on raconte, à la maison.
+narrateur|Le ventre de Nina se desserre, tout doucement.
+enfant-f|Merci, papa. Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4510,7 +4751,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué au bac à sable. Elle a pris le seau. Mila est venue. Le sable est resté froid, tout calme. J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. On t'a écoutée. Si malaise, tu reviens nous le dire. Le gant rouge est presque sec. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4650,7 +4891,17 @@
       <c r="AV21" s="2" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a joué au bac à sable.
+narrateur|Elle a pris le seau.
+narrateur|Mila est venue.
+narrateur|Le sable est resté froid, tout calme.
+enfant-f|J'ai écouté. Puis j'ai raconté.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+maman|On t'a écoutée.
+maman|Si malaise, tu reviens nous le dire.
+narrateur|Le gant rouge est presque sec.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr"/>
@@ -4678,7 +4929,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint Sami. Un chat miaule une fois. On range un objet. Cette fin-là est celle de le bac à sable, le seau et Sami. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
+          <t>Raphaël pose son bâton près du seau. Une fourmi passe au bord. Nina souffle le sable, tout doux. Nina est au bac à sable. Elle a le seau. Bonjour, Raphaël. Bonjour, Nina. J'ai raconté mon malaise. Oui. Tu as écouté, puis raconté. Si malaise, raconter à la maison. Tu as parlé à maman ? Oui. Et à papa. On écoute la maîtresse. Puis on raconte, à la maison. Le ventre de Nina se desserre, tout doucement. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4818,10 +5069,29 @@
       <c r="AV22" s="2" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>narrateur|Noé rejoint Sami. Un chat miaule une fois. On range un objet. Cette fin-là est celle de le bac à sable, le seau et Sami. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr"/>
+          <t>narrateur|Raphaël pose son bâton près du seau.
+narrateur|Une fourmi passe au bord.
+narrateur|Nina souffle le sable, tout doux.
+narrateur|Nina est au bac à sable.
+narrateur|Elle a le seau.
+enfant-f|Bonjour, Raphaël.
+enfant-m|Bonjour, Nina.
+enfant-f|J'ai raconté mon malaise.
+papa|Oui. Tu as écouté, puis raconté.
+maman|Si malaise, raconter à la maison.
+enfant-m|Tu as parlé à maman ?
+enfant-f|Oui. Et à papa.
+papa|On écoute la maîtresse.
+maman|Puis on raconte, à la maison.
+narrateur|Le ventre de Nina se desserre, tout doucement.
+enfant-f|Merci, papa. Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4846,7 +5116,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué au bac à sable. Elle a pris le seau. Raphaël est venu. Le sable est resté froid, tout calme. J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. On t'a écoutée. Si malaise, tu reviens nous le dire. Le gant rouge est presque sec. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -4986,7 +5256,17 @@
       <c r="AV23" s="2" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a joué au bac à sable.
+narrateur|Elle a pris le seau.
+narrateur|Raphaël est venu.
+narrateur|Le sable est resté froid, tout calme.
+enfant-f|J'ai écouté. Puis j'ai raconté.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+maman|On t'a écoutée.
+maman|Si malaise, tu reviens nous le dire.
+narrateur|Le gant rouge est presque sec.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr"/>
@@ -5014,7 +5294,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Noé a choisi le doudou. L'eau coule, tout petit bruit. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé répète tout bas : écouter, si malaise raconter à la maison. On écoute jusqu'au bout. papa n'est pas loin.</t>
+          <t>Plus tard, Nina prend le doudou. Le doudou a du sable à l'oreille. Nina pense encore au bac à sable. Papa s'assoit sur le banc. J'ai un malaise. Je raconte à la maison. On t'écoute. Un camarade a chuchoté, à l'école. Tu as écouté la maîtresse. Puis tu nous as dit. Si malaise, tu racontes à la maison. Bravo, Nina. Tu as fait du bon travail. Le doudou est doux, un peu froissé. Tu veux rester un peu ? Oui.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5154,10 +5434,28 @@
       <c r="AV24" s="2" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>narrateur|Noé a choisi le doudou. L'eau coule, tout petit bruit. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé répète tout bas : écouter, si malaise raconter à la maison. On écoute jusqu'au bout. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr"/>
+          <t>narrateur|Plus tard, Nina prend le doudou.
+narrateur|Le doudou a du sable à l'oreille.
+narrateur|Nina pense encore au bac à sable.
+narrateur|Papa s'assoit sur le banc.
+enfant-f|J'ai un malaise.
+enfant-f|Je raconte à la maison.
+maman|On t'écoute.
+enfant-f|Un camarade a chuchoté, à l'école.
+papa|Tu as écouté la maîtresse.
+papa|Puis tu nous as dit.
+maman|Si malaise, tu racontes à la maison.
+papa|Bravo, Nina. Tu as fait du bon travail.
+narrateur|Le doudou est doux, un peu froissé.
+maman|Tu veux rester un peu ?
+enfant-f|Oui.</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>doudou</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5182,7 +5480,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Qui arrive, au parc ? Nino, Mila, ou Raphaël.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -5350,7 +5648,8 @@
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Qui arrive, au parc ?
+maman|Nino, Mila, ou Raphaël.</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr"/>
@@ -5378,7 +5677,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint Tom. Il y a des miettes sur la table. On se tait une seconde. Cette fin-là est celle de le bac à sable, le doudou et Tom. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
+          <t>Nino voit le doudou dans le sable. Il le tend, tout soigneux. Tiens. Nina est au bac à sable. Elle a le doudou. Bonjour, Nino. Bonjour, Nina. J'ai raconté mon malaise. Oui. Tu as écouté, puis raconté. Si malaise, raconter à la maison. Tu as parlé à maman ? Oui. Et à papa. On écoute la maîtresse. Puis on raconte, à la maison. Le ventre de Nina se desserre, tout doucement. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5518,10 +5817,29 @@
       <c r="AV26" s="2" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>narrateur|Noé rejoint Tom. Il y a des miettes sur la table. On se tait une seconde. Cette fin-là est celle de le bac à sable, le doudou et Tom. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr"/>
+          <t>narrateur|Nino voit le doudou dans le sable.
+narrateur|Il le tend, tout soigneux.
+enfant-m|Tiens.
+narrateur|Nina est au bac à sable.
+narrateur|Elle a le doudou.
+enfant-f|Bonjour, Nino.
+enfant-m|Bonjour, Nina.
+enfant-f|J'ai raconté mon malaise.
+papa|Oui. Tu as écouté, puis raconté.
+maman|Si malaise, raconter à la maison.
+enfant-m|Tu as parlé à maman ?
+enfant-f|Oui. Et à papa.
+papa|On écoute la maîtresse.
+maman|Puis on raconte, à la maison.
+narrateur|Le ventre de Nina se desserre, tout doucement.
+enfant-f|Merci, papa. Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5546,7 +5864,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué au bac à sable. Elle a pris le doudou. Nino est venu. Le sable est resté froid, tout calme. J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. On t'a écoutée. Si malaise, tu reviens nous le dire. Le gant rouge est presque sec. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -5686,7 +6004,17 @@
       <c r="AV27" s="2" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a joué au bac à sable.
+narrateur|Elle a pris le doudou.
+narrateur|Nino est venu.
+narrateur|Le sable est resté froid, tout calme.
+enfant-f|J'ai écouté. Puis j'ai raconté.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+maman|On t'a écoutée.
+maman|Si malaise, tu reviens nous le dire.
+narrateur|Le gant rouge est presque sec.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr"/>
@@ -5714,7 +6042,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint Léa. Un chat miaule une fois. On se tient la main. Cette fin-là est celle de le bac à sable, le doudou et Léa. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
+          <t>Mila caresse l'oreille du doudou. Un grain de sable tombe. Nina le serre contre elle. Nina est au bac à sable. Elle a le doudou. Bonjour, Mila. Bonjour, Nina. J'ai raconté mon malaise. Oui. Tu as écouté, puis raconté. Si malaise, raconter à la maison. Tu as parlé à maman ? Oui. Et à papa. On écoute la maîtresse. Puis on raconte, à la maison. Le ventre de Nina se desserre, tout doucement. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5854,10 +6182,29 @@
       <c r="AV28" s="2" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>narrateur|Noé rejoint Léa. Un chat miaule une fois. On se tient la main. Cette fin-là est celle de le bac à sable, le doudou et Léa. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX28" t="inlineStr"/>
+          <t>narrateur|Mila caresse l'oreille du doudou.
+narrateur|Un grain de sable tombe.
+narrateur|Nina le serre contre elle.
+narrateur|Nina est au bac à sable.
+narrateur|Elle a le doudou.
+enfant-f|Bonjour, Mila.
+enfant-f|Bonjour, Nina.
+enfant-f|J'ai raconté mon malaise.
+papa|Oui. Tu as écouté, puis raconté.
+maman|Si malaise, raconter à la maison.
+enfant-f|Tu as parlé à maman ?
+enfant-f|Oui. Et à papa.
+papa|On écoute la maîtresse.
+maman|Puis on raconte, à la maison.
+narrateur|Le ventre de Nina se desserre, tout doucement.
+enfant-f|Merci, papa. Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5882,7 +6229,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué au bac à sable. Elle a pris le doudou. Mila est venue. Le sable est resté froid, tout calme. J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. On t'a écoutée. Si malaise, tu reviens nous le dire. Le gant rouge est presque sec. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6022,7 +6369,17 @@
       <c r="AV29" s="2" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a joué au bac à sable.
+narrateur|Elle a pris le doudou.
+narrateur|Mila est venue.
+narrateur|Le sable est resté froid, tout calme.
+enfant-f|J'ai écouté. Puis j'ai raconté.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+maman|On t'a écoutée.
+maman|Si malaise, tu reviens nous le dire.
+narrateur|Le gant rouge est presque sec.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr"/>
@@ -6050,7 +6407,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint Sami. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de le bac à sable, le doudou et Sami. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
+          <t>Raphaël assied le doudou sur le seau. Le doudou penche, tout drôle. Nina rit, tout bas. Nina est au bac à sable. Elle a le doudou. Bonjour, Raphaël. Bonjour, Nina. J'ai raconté mon malaise. Oui. Tu as écouté, puis raconté. Si malaise, raconter à la maison. Tu as parlé à maman ? Oui. Et à papa. On écoute la maîtresse. Puis on raconte, à la maison. Le ventre de Nina se desserre, tout doucement. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6190,10 +6547,29 @@
       <c r="AV30" s="2" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>narrateur|Noé rejoint Sami. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de le bac à sable, le doudou et Sami. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr"/>
+          <t>narrateur|Raphaël assied le doudou sur le seau.
+narrateur|Le doudou penche, tout drôle.
+narrateur|Nina rit, tout bas.
+narrateur|Nina est au bac à sable.
+narrateur|Elle a le doudou.
+enfant-f|Bonjour, Raphaël.
+enfant-m|Bonjour, Nina.
+enfant-f|J'ai raconté mon malaise.
+papa|Oui. Tu as écouté, puis raconté.
+maman|Si malaise, raconter à la maison.
+enfant-m|Tu as parlé à maman ?
+enfant-f|Oui. Et à papa.
+papa|On écoute la maîtresse.
+maman|Puis on raconte, à la maison.
+narrateur|Le ventre de Nina se desserre, tout doucement.
+enfant-f|Merci, papa. Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6218,7 +6594,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué au bac à sable. Elle a pris le doudou. Raphaël est venu. Le sable est resté froid, tout calme. J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. On t'a écoutée. Si malaise, tu reviens nous le dire. Le gant rouge est presque sec. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6358,7 +6734,17 @@
       <c r="AV31" s="2" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a joué au bac à sable.
+narrateur|Elle a pris le doudou.
+narrateur|Raphaël est venu.
+narrateur|Le sable est resté froid, tout calme.
+enfant-f|J'ai écouté. Puis j'ai raconté.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+maman|On t'a écoutée.
+maman|Si malaise, tu reviens nous le dire.
+narrateur|Le gant rouge est presque sec.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr"/>
@@ -6386,7 +6772,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Noé va vers le toboggan. Le vent est doux. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Noé se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On se tient la main. Je suis là. On reste ensemble.</t>
+          <t>Nina va vers le toboggan. Le métal est froid sous la main. Une feuille collée brille, toute plate. Elle a écouté la maîtresse, à l'école. Son ventre est encore serré. C'est un malaise. Oui. Tu le diras à la maison. Papa aussi ? Moi aussi. Je suis là. On écoute la maîtresse. Si malaise, raconter à la maison. Nina monte une marche, tout doux. Tu veux que je tienne ta main ? Oui. Bravo. Tu as parlé de ton ventre.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6526,11 +6912,28 @@
       <c r="AV32" s="2" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>narrateur|Noé va vers le toboggan. Le vent est doux. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Noé se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On se tient la main.
-maman|Je suis là. On reste ensemble.</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr"/>
+          <t>narrateur|Nina va vers le toboggan.
+narrateur|Le métal est froid sous la main.
+narrateur|Une feuille collée brille, toute plate.
+narrateur|Elle a écouté la maîtresse, à l'école.
+narrateur|Son ventre est encore serré.
+enfant-f|C'est un malaise.
+maman|Oui. Tu le diras à la maison.
+enfant-f|Papa aussi ?
+papa|Moi aussi. Je suis là.
+maman|On écoute la maîtresse.
+maman|Si malaise, raconter à la maison.
+narrateur|Nina monte une marche, tout doux.
+papa|Tu veux que je tienne ta main ?
+enfant-f|Oui.
+maman|Bravo. Tu as parlé de ton ventre.</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>toboggan</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6555,7 +6958,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
+          <t>Un malaise : on raconte à la maison ?</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -6715,7 +7118,7 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
+          <t>narrateur|Un malaise : on raconte à la maison ?</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr"/>
@@ -6743,7 +7146,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé respire. Noé retient : écouter, si malaise raconter à la maison. On continue, avec maman.</t>
+          <t>Oui. Si malaise, tu racontes à la maison. On écoute aussi la maîtresse. Nina tient la rampe, tout calme. Bravo. Tu as parlé. Papa écoutera. Oui. J'écoute.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6887,7 +7290,13 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé respire. Noé retient : écouter, si malaise raconter à la maison. On continue, avec maman.</t>
+          <t>narrateur|Oui.
+papa|Si malaise, tu racontes à la maison.
+maman|On écoute aussi la maîtresse.
+narrateur|Nina tient la rampe, tout calme.
+maman|Bravo. Tu as parlé.
+enfant-f|Papa écoutera.
+papa|Oui. J'écoute.</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr"/>
@@ -6915,7 +7324,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>Nina prend quoi ? Le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -7079,7 +7488,8 @@
       <c r="AV35" s="2" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>narrateur|Nina prend quoi ?
+papa|Le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr"/>
@@ -7107,7 +7517,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Noé a choisi le ballon. Un vélo passe au loin. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé répète tout bas : écouter, si malaise raconter à la maison. On dit merci. papa n'est pas loin.</t>
+          <t>Plus tard, Nina prend le ballon. Le ballon rebondit près du toboggan. Elle est encore au toboggan. J'ai écouté la maîtresse. J'ai un malaise. Tu as bien fait de raconter. Tu as écouté, à l'école. Si malaise, tu viens nous le dire. Je raconte à la maison. Bravo, Nina. C'est du bon travail. Le ballon est un peu froid. Je t'écoute. On reste un moment.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7247,10 +7657,26 @@
       <c r="AV36" s="2" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>narrateur|Noé a choisi le ballon. Un vélo passe au loin. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé répète tout bas : écouter, si malaise raconter à la maison. On dit merci. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr"/>
+          <t>narrateur|Plus tard, Nina prend le ballon.
+narrateur|Le ballon rebondit près du toboggan.
+narrateur|Elle est encore au toboggan.
+enfant-f|J'ai écouté la maîtresse.
+enfant-f|J'ai un malaise.
+papa|Tu as bien fait de raconter.
+maman|Tu as écouté, à l'école.
+papa|Si malaise, tu viens nous le dire.
+enfant-f|Je raconte à la maison.
+maman|Bravo, Nina.
+maman|C'est du bon travail.
+narrateur|Le ballon est un peu froid.
+papa|Je t'écoute. On reste un moment.</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>ballon</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7275,7 +7701,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Qui arrive, au parc ? Nino, Mila, ou Raphaël.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -7443,7 +7869,8 @@
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Qui arrive, au parc ?
+maman|Nino, Mila, ou Raphaël.</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr"/>
@@ -7471,7 +7898,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint Tom. La lumière est claire. On se tient la main. Cette fin-là est celle de le toboggan, le ballon et Tom. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
+          <t>Nino attend en bas du toboggan. Le ballon est sous son bras. Nina descend, tout doux. Nina est au toboggan. Elle a le ballon. Bonjour, Nino. Bonjour, Nina. J'ai raconté mon malaise. Oui. Tu as écouté, puis raconté. Si malaise, raconter à la maison. Tu as parlé à maman ? Oui. Et à papa. On écoute la maîtresse. Puis on raconte, à la maison. Le ventre de Nina se desserre, tout doucement. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7611,10 +8038,29 @@
       <c r="AV38" s="2" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>narrateur|Noé rejoint Tom. La lumière est claire. On se tient la main. Cette fin-là est celle de le toboggan, le ballon et Tom. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr"/>
+          <t>narrateur|Nino attend en bas du toboggan.
+narrateur|Le ballon est sous son bras.
+narrateur|Nina descend, tout doux.
+narrateur|Nina est au toboggan.
+narrateur|Elle a le ballon.
+enfant-f|Bonjour, Nino.
+enfant-m|Bonjour, Nina.
+enfant-f|J'ai raconté mon malaise.
+papa|Oui. Tu as écouté, puis raconté.
+maman|Si malaise, raconter à la maison.
+enfant-m|Tu as parlé à maman ?
+enfant-f|Oui. Et à papa.
+papa|On écoute la maîtresse.
+maman|Puis on raconte, à la maison.
+narrateur|Le ventre de Nina se desserre, tout doucement.
+enfant-f|Merci, papa. Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7639,7 +8085,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué au toboggan. Elle a pris le ballon. Nino est venu. Le toboggan a gardé sa feuille. J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. On t'a écoutée. Si malaise, tu reviens nous le dire. Le gant rouge est presque sec. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -7779,7 +8225,17 @@
       <c r="AV39" s="2" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a joué au toboggan.
+narrateur|Elle a pris le ballon.
+narrateur|Nino est venu.
+narrateur|Le toboggan a gardé sa feuille.
+enfant-f|J'ai écouté. Puis j'ai raconté.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+maman|On t'a écoutée.
+maman|Si malaise, tu reviens nous le dire.
+narrateur|Le gant rouge est presque sec.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr"/>
@@ -7807,7 +8263,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint Léa. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de le toboggan, le ballon et Léa. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
+          <t>Mila tient le ballon en haut. Le métal brille sous ses mains. Nina pose un pied, puis l'autre. Nina est au toboggan. Elle a le ballon. Bonjour, Mila. Bonjour, Nina. J'ai raconté mon malaise. Oui. Tu as écouté, puis raconté. Si malaise, raconter à la maison. Tu as parlé à maman ? Oui. Et à papa. On écoute la maîtresse. Puis on raconte, à la maison. Le ventre de Nina se desserre, tout doucement. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7947,10 +8403,29 @@
       <c r="AV40" s="2" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>narrateur|Noé rejoint Léa. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de le toboggan, le ballon et Léa. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX40" t="inlineStr"/>
+          <t>narrateur|Mila tient le ballon en haut.
+narrateur|Le métal brille sous ses mains.
+narrateur|Nina pose un pied, puis l'autre.
+narrateur|Nina est au toboggan.
+narrateur|Elle a le ballon.
+enfant-f|Bonjour, Mila.
+enfant-f|Bonjour, Nina.
+enfant-f|J'ai raconté mon malaise.
+papa|Oui. Tu as écouté, puis raconté.
+maman|Si malaise, raconter à la maison.
+enfant-f|Tu as parlé à maman ?
+enfant-f|Oui. Et à papa.
+papa|On écoute la maîtresse.
+maman|Puis on raconte, à la maison.
+narrateur|Le ventre de Nina se desserre, tout doucement.
+enfant-f|Merci, papa. Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7975,7 +8450,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué au toboggan. Elle a pris le ballon. Mila est venue. Le toboggan a gardé sa feuille. J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. On t'a écoutée. Si malaise, tu reviens nous le dire. Le gant rouge est presque sec. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -8115,7 +8590,17 @@
       <c r="AV41" s="2" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a joué au toboggan.
+narrateur|Elle a pris le ballon.
+narrateur|Mila est venue.
+narrateur|Le toboggan a gardé sa feuille.
+enfant-f|J'ai écouté. Puis j'ai raconté.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+maman|On t'a écoutée.
+maman|Si malaise, tu reviens nous le dire.
+narrateur|Le gant rouge est presque sec.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr"/>
@@ -8143,7 +8628,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint Sami. Un chat miaule une fois. On dit merci. Cette fin-là est celle de le toboggan, le ballon et Sami. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
+          <t>Raphaël fait rouler le ballon au pied. Nina glisse, les joues froides. Le vent est doux. Nina est au toboggan. Elle a le ballon. Bonjour, Raphaël. Bonjour, Nina. J'ai raconté mon malaise. Oui. Tu as écouté, puis raconté. Si malaise, raconter à la maison. Tu as parlé à maman ? Oui. Et à papa. On écoute la maîtresse. Puis on raconte, à la maison. Le ventre de Nina se desserre, tout doucement. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8283,10 +8768,29 @@
       <c r="AV42" s="2" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>narrateur|Noé rejoint Sami. Un chat miaule une fois. On dit merci. Cette fin-là est celle de le toboggan, le ballon et Sami. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr"/>
+          <t>narrateur|Raphaël fait rouler le ballon au pied.
+narrateur|Nina glisse, les joues froides.
+narrateur|Le vent est doux.
+narrateur|Nina est au toboggan.
+narrateur|Elle a le ballon.
+enfant-f|Bonjour, Raphaël.
+enfant-m|Bonjour, Nina.
+enfant-f|J'ai raconté mon malaise.
+papa|Oui. Tu as écouté, puis raconté.
+maman|Si malaise, raconter à la maison.
+enfant-m|Tu as parlé à maman ?
+enfant-f|Oui. Et à papa.
+papa|On écoute la maîtresse.
+maman|Puis on raconte, à la maison.
+narrateur|Le ventre de Nina se desserre, tout doucement.
+enfant-f|Merci, papa. Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8311,7 +8815,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué au toboggan. Elle a pris le ballon. Raphaël est venu. Le toboggan a gardé sa feuille. J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. On t'a écoutée. Si malaise, tu reviens nous le dire. Le gant rouge est presque sec. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -8451,7 +8955,17 @@
       <c r="AV43" s="2" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a joué au toboggan.
+narrateur|Elle a pris le ballon.
+narrateur|Raphaël est venu.
+narrateur|Le toboggan a gardé sa feuille.
+enfant-f|J'ai écouté. Puis j'ai raconté.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+maman|On t'a écoutée.
+maman|Si malaise, tu reviens nous le dire.
+narrateur|Le gant rouge est presque sec.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr"/>
@@ -8479,7 +8993,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Noé a choisi le seau. La lumière est claire. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé répète tout bas : écouter, si malaise raconter à la maison. On souffle doucement. papa n'est pas loin.</t>
+          <t>Plus tard, Nina prend le seau. Le seau a une feuille dedans. Elle pense encore au toboggan. J'ai écouté la maîtresse. J'ai eu un malaise. Raconte. On est là. Un camarade a parlé tout bas. Tu as bien fait de le dire. À la maison. On écoute la maîtresse. Si malaise, raconter à papa ou maman. Bravo. Ton ventre peut se desserrer. Une goutte glisse du bord du seau. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8619,10 +9133,27 @@
       <c r="AV44" s="2" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>narrateur|Noé a choisi le seau. La lumière est claire. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé répète tout bas : écouter, si malaise raconter à la maison. On souffle doucement. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr"/>
+          <t>narrateur|Plus tard, Nina prend le seau.
+narrateur|Le seau a une feuille dedans.
+narrateur|Elle pense encore au toboggan.
+enfant-f|J'ai écouté la maîtresse.
+enfant-f|J'ai eu un malaise.
+papa|Raconte. On est là.
+enfant-f|Un camarade a parlé tout bas.
+maman|Tu as bien fait de le dire.
+maman|À la maison.
+papa|On écoute la maîtresse.
+papa|Si malaise, raconter à papa ou maman.
+maman|Bravo. Ton ventre peut se desserrer.
+narrateur|Une goutte glisse du bord du seau.
+enfant-f|Merci, papa. Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>seau</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8647,7 +9178,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Qui arrive, au parc ? Nino, Mila, ou Raphaël.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -8815,7 +9346,8 @@
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Qui arrive, au parc ?
+maman|Nino, Mila, ou Raphaël.</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr"/>
@@ -8843,7 +9375,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint Tom. Il y a des miettes sur la table. On se tient la main. Cette fin-là est celle de le toboggan, le seau et Tom. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
+          <t>Nino a mis le seau en bas. Comme un panier, tout rouge. Nina arrive près de lui. Nina est au toboggan. Elle a le seau. Bonjour, Nino. Bonjour, Nina. J'ai raconté mon malaise. Oui. Tu as écouté, puis raconté. Si malaise, raconter à la maison. Tu as parlé à maman ? Oui. Et à papa. On écoute la maîtresse. Puis on raconte, à la maison. Le ventre de Nina se desserre, tout doucement. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8983,10 +9515,29 @@
       <c r="AV46" s="2" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>narrateur|Noé rejoint Tom. Il y a des miettes sur la table. On se tient la main. Cette fin-là est celle de le toboggan, le seau et Tom. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX46" t="inlineStr"/>
+          <t>narrateur|Nino a mis le seau en bas.
+narrateur|Comme un panier, tout rouge.
+narrateur|Nina arrive près de lui.
+narrateur|Nina est au toboggan.
+narrateur|Elle a le seau.
+enfant-f|Bonjour, Nino.
+enfant-m|Bonjour, Nina.
+enfant-f|J'ai raconté mon malaise.
+papa|Oui. Tu as écouté, puis raconté.
+maman|Si malaise, raconter à la maison.
+enfant-m|Tu as parlé à maman ?
+enfant-f|Oui. Et à papa.
+papa|On écoute la maîtresse.
+maman|Puis on raconte, à la maison.
+narrateur|Le ventre de Nina se desserre, tout doucement.
+enfant-f|Merci, papa. Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9011,7 +9562,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué au toboggan. Elle a pris le seau. Nino est venu. Le toboggan a gardé sa feuille. J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. On t'a écoutée. Si malaise, tu reviens nous le dire. Le gant rouge est presque sec. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9151,7 +9702,17 @@
       <c r="AV47" s="2" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a joué au toboggan.
+narrateur|Elle a pris le seau.
+narrateur|Nino est venu.
+narrateur|Le toboggan a gardé sa feuille.
+enfant-f|J'ai écouté. Puis j'ai raconté.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+maman|On t'a écoutée.
+maman|Si malaise, tu reviens nous le dire.
+narrateur|Le gant rouge est presque sec.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr"/>
@@ -9179,7 +9740,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint Léa. Un chat miaule une fois. On range un objet. Cette fin-là est celle de le toboggan, le seau et Léa. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
+          <t>Mila a une feuille dans le seau. Nina la retire, tout calme. On dirait un bateau. Nina est au toboggan. Elle a le seau. Bonjour, Mila. Bonjour, Nina. J'ai raconté mon malaise. Oui. Tu as écouté, puis raconté. Si malaise, raconter à la maison. Tu as parlé à maman ? Oui. Et à papa. On écoute la maîtresse. Puis on raconte, à la maison. Le ventre de Nina se desserre, tout doucement. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9319,10 +9880,29 @@
       <c r="AV48" s="2" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>narrateur|Noé rejoint Léa. Un chat miaule une fois. On range un objet. Cette fin-là est celle de le toboggan, le seau et Léa. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX48" t="inlineStr"/>
+          <t>narrateur|Mila a une feuille dans le seau.
+narrateur|Nina la retire, tout calme.
+narrateur|On dirait un bateau.
+narrateur|Nina est au toboggan.
+narrateur|Elle a le seau.
+enfant-f|Bonjour, Mila.
+enfant-f|Bonjour, Nina.
+enfant-f|J'ai raconté mon malaise.
+papa|Oui. Tu as écouté, puis raconté.
+maman|Si malaise, raconter à la maison.
+enfant-f|Tu as parlé à maman ?
+enfant-f|Oui. Et à papa.
+papa|On écoute la maîtresse.
+maman|Puis on raconte, à la maison.
+narrateur|Le ventre de Nina se desserre, tout doucement.
+enfant-f|Merci, papa. Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9347,7 +9927,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué au toboggan. Elle a pris le seau. Mila est venue. Le toboggan a gardé sa feuille. J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. On t'a écoutée. Si malaise, tu reviens nous le dire. Le gant rouge est presque sec. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9487,7 +10067,17 @@
       <c r="AV49" s="2" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a joué au toboggan.
+narrateur|Elle a pris le seau.
+narrateur|Mila est venue.
+narrateur|Le toboggan a gardé sa feuille.
+enfant-f|J'ai écouté. Puis j'ai raconté.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+maman|On t'a écoutée.
+maman|Si malaise, tu reviens nous le dire.
+narrateur|Le gant rouge est presque sec.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr"/>
@@ -9515,7 +10105,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint Sami. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de le toboggan, le seau et Sami. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
+          <t>Raphaël tape le seau, tout léger. Ça fait un petit bruit rond. Nina écoute, les yeux ronds. Nina est au toboggan. Elle a le seau. Bonjour, Raphaël. Bonjour, Nina. J'ai raconté mon malaise. Oui. Tu as écouté, puis raconté. Si malaise, raconter à la maison. Tu as parlé à maman ? Oui. Et à papa. On écoute la maîtresse. Puis on raconte, à la maison. Le ventre de Nina se desserre, tout doucement. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9655,10 +10245,29 @@
       <c r="AV50" s="2" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>narrateur|Noé rejoint Sami. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de le toboggan, le seau et Sami. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX50" t="inlineStr"/>
+          <t>narrateur|Raphaël tape le seau, tout léger.
+narrateur|Ça fait un petit bruit rond.
+narrateur|Nina écoute, les yeux ronds.
+narrateur|Nina est au toboggan.
+narrateur|Elle a le seau.
+enfant-f|Bonjour, Raphaël.
+enfant-m|Bonjour, Nina.
+enfant-f|J'ai raconté mon malaise.
+papa|Oui. Tu as écouté, puis raconté.
+maman|Si malaise, raconter à la maison.
+enfant-m|Tu as parlé à maman ?
+enfant-f|Oui. Et à papa.
+papa|On écoute la maîtresse.
+maman|Puis on raconte, à la maison.
+narrateur|Le ventre de Nina se desserre, tout doucement.
+enfant-f|Merci, papa. Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9683,7 +10292,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué au toboggan. Elle a pris le seau. Raphaël est venu. Le toboggan a gardé sa feuille. J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. On t'a écoutée. Si malaise, tu reviens nous le dire. Le gant rouge est presque sec. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -9823,7 +10432,17 @@
       <c r="AV51" s="2" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a joué au toboggan.
+narrateur|Elle a pris le seau.
+narrateur|Raphaël est venu.
+narrateur|Le toboggan a gardé sa feuille.
+enfant-f|J'ai écouté. Puis j'ai raconté.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+maman|On t'a écoutée.
+maman|Si malaise, tu reviens nous le dire.
+narrateur|Le gant rouge est presque sec.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr"/>
@@ -9851,7 +10470,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Noé a choisi le doudou. Il y a des miettes sur la table. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé répète tout bas : écouter, si malaise raconter à la maison. On écoute jusqu'au bout. papa n'est pas loin.</t>
+          <t>Plus tard, Nina prend le doudou. Le doudou sent encore le manteau. Nina pense encore au toboggan. Papa s'assoit sur le banc. J'ai un malaise. Je raconte à la maison. On t'écoute. Un camarade a chuchoté, à l'école. Tu as écouté la maîtresse. Puis tu nous as dit. Si malaise, tu racontes à la maison. Bravo, Nina. Tu as fait du bon travail. Le doudou est doux, un peu froissé. Tu veux rester un peu ? Oui.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9991,10 +10610,28 @@
       <c r="AV52" s="2" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|Noé a choisi le doudou. Il y a des miettes sur la table. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé répète tout bas : écouter, si malaise raconter à la maison. On écoute jusqu'au bout. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX52" t="inlineStr"/>
+          <t>narrateur|Plus tard, Nina prend le doudou.
+narrateur|Le doudou sent encore le manteau.
+narrateur|Nina pense encore au toboggan.
+narrateur|Papa s'assoit sur le banc.
+enfant-f|J'ai un malaise.
+enfant-f|Je raconte à la maison.
+maman|On t'écoute.
+enfant-f|Un camarade a chuchoté, à l'école.
+papa|Tu as écouté la maîtresse.
+papa|Puis tu nous as dit.
+maman|Si malaise, tu racontes à la maison.
+papa|Bravo, Nina. Tu as fait du bon travail.
+narrateur|Le doudou est doux, un peu froissé.
+maman|Tu veux rester un peu ?
+enfant-f|Oui.</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>doudou</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10019,7 +10656,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Qui arrive, au parc ? Nino, Mila, ou Raphaël.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -10187,7 +10824,8 @@
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Qui arrive, au parc ?
+maman|Nino, Mila, ou Raphaël.</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr"/>
@@ -10215,7 +10853,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint Tom. Un chat miaule une fois. On se tient la main. Cette fin-là est celle de le toboggan, le doudou et Tom. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
+          <t>Nino a le doudou sur les genoux. Il est en bas du toboggan. Nina le reprend, tout doux. Nina est au toboggan. Elle a le doudou. Bonjour, Nino. Bonjour, Nina. J'ai raconté mon malaise. Oui. Tu as écouté, puis raconté. Si malaise, raconter à la maison. Tu as parlé à maman ? Oui. Et à papa. On écoute la maîtresse. Puis on raconte, à la maison. Le ventre de Nina se desserre, tout doucement. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10355,10 +10993,29 @@
       <c r="AV54" s="2" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>narrateur|Noé rejoint Tom. Un chat miaule une fois. On se tient la main. Cette fin-là est celle de le toboggan, le doudou et Tom. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX54" t="inlineStr"/>
+          <t>narrateur|Nino a le doudou sur les genoux.
+narrateur|Il est en bas du toboggan.
+narrateur|Nina le reprend, tout doux.
+narrateur|Nina est au toboggan.
+narrateur|Elle a le doudou.
+enfant-f|Bonjour, Nino.
+enfant-m|Bonjour, Nina.
+enfant-f|J'ai raconté mon malaise.
+papa|Oui. Tu as écouté, puis raconté.
+maman|Si malaise, raconter à la maison.
+enfant-m|Tu as parlé à maman ?
+enfant-f|Oui. Et à papa.
+papa|On écoute la maîtresse.
+maman|Puis on raconte, à la maison.
+narrateur|Le ventre de Nina se desserre, tout doucement.
+enfant-f|Merci, papa. Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10383,7 +11040,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué au toboggan. Elle a pris le doudou. Nino est venu. Le toboggan a gardé sa feuille. J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. On t'a écoutée. Si malaise, tu reviens nous le dire. Le gant rouge est presque sec. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -10523,7 +11180,17 @@
       <c r="AV55" s="2" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a joué au toboggan.
+narrateur|Elle a pris le doudou.
+narrateur|Nino est venu.
+narrateur|Le toboggan a gardé sa feuille.
+enfant-f|J'ai écouté. Puis j'ai raconté.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+maman|On t'a écoutée.
+maman|Si malaise, tu reviens nous le dire.
+narrateur|Le gant rouge est presque sec.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr"/>
@@ -10551,7 +11218,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint Léa. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de le toboggan, le doudou et Léa. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
+          <t>Mila pose le doudou sur une marche. Il attend, tout sage. Nina le prend avant de glisser. Nina est au toboggan. Elle a le doudou. Bonjour, Mila. Bonjour, Nina. J'ai raconté mon malaise. Oui. Tu as écouté, puis raconté. Si malaise, raconter à la maison. Tu as parlé à maman ? Oui. Et à papa. On écoute la maîtresse. Puis on raconte, à la maison. Le ventre de Nina se desserre, tout doucement. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10691,10 +11358,29 @@
       <c r="AV56" s="2" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>narrateur|Noé rejoint Léa. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de le toboggan, le doudou et Léa. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX56" t="inlineStr"/>
+          <t>narrateur|Mila pose le doudou sur une marche.
+narrateur|Il attend, tout sage.
+narrateur|Nina le prend avant de glisser.
+narrateur|Nina est au toboggan.
+narrateur|Elle a le doudou.
+enfant-f|Bonjour, Mila.
+enfant-f|Bonjour, Nina.
+enfant-f|J'ai raconté mon malaise.
+papa|Oui. Tu as écouté, puis raconté.
+maman|Si malaise, raconter à la maison.
+enfant-f|Tu as parlé à maman ?
+enfant-f|Oui. Et à papa.
+papa|On écoute la maîtresse.
+maman|Puis on raconte, à la maison.
+narrateur|Le ventre de Nina se desserre, tout doucement.
+enfant-f|Merci, papa. Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10719,7 +11405,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué au toboggan. Elle a pris le doudou. Mila est venue. Le toboggan a gardé sa feuille. J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. On t'a écoutée. Si malaise, tu reviens nous le dire. Le gant rouge est presque sec. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -10859,7 +11545,17 @@
       <c r="AV57" s="2" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a joué au toboggan.
+narrateur|Elle a pris le doudou.
+narrateur|Mila est venue.
+narrateur|Le toboggan a gardé sa feuille.
+enfant-f|J'ai écouté. Puis j'ai raconté.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+maman|On t'a écoutée.
+maman|Si malaise, tu reviens nous le dire.
+narrateur|Le gant rouge est presque sec.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr"/>
@@ -10887,7 +11583,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint Sami. La couverture est douce. On dit merci. Cette fin-là est celle de le toboggan, le doudou et Sami. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
+          <t>Raphaël tient le doudou, tout haut. Pour qu'il voie le ciel dans la flaque. Nina dit merci, tout bas. Nina est au toboggan. Elle a le doudou. Bonjour, Raphaël. Bonjour, Nina. J'ai raconté mon malaise. Oui. Tu as écouté, puis raconté. Si malaise, raconter à la maison. Tu as parlé à maman ? Oui. Et à papa. On écoute la maîtresse. Puis on raconte, à la maison. Le ventre de Nina se desserre, tout doucement. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -11027,10 +11723,29 @@
       <c r="AV58" s="2" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>narrateur|Noé rejoint Sami. La couverture est douce. On dit merci. Cette fin-là est celle de le toboggan, le doudou et Sami. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX58" t="inlineStr"/>
+          <t>narrateur|Raphaël tient le doudou, tout haut.
+narrateur|Pour qu'il voie le ciel dans la flaque.
+narrateur|Nina dit merci, tout bas.
+narrateur|Nina est au toboggan.
+narrateur|Elle a le doudou.
+enfant-f|Bonjour, Raphaël.
+enfant-m|Bonjour, Nina.
+enfant-f|J'ai raconté mon malaise.
+papa|Oui. Tu as écouté, puis raconté.
+maman|Si malaise, raconter à la maison.
+enfant-m|Tu as parlé à maman ?
+enfant-f|Oui. Et à papa.
+papa|On écoute la maîtresse.
+maman|Puis on raconte, à la maison.
+narrateur|Le ventre de Nina se desserre, tout doucement.
+enfant-f|Merci, papa. Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11055,7 +11770,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué au toboggan. Elle a pris le doudou. Raphaël est venu. Le toboggan a gardé sa feuille. J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. On t'a écoutée. Si malaise, tu reviens nous le dire. Le gant rouge est presque sec. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -11195,7 +11910,17 @@
       <c r="AV59" s="2" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a joué au toboggan.
+narrateur|Elle a pris le doudou.
+narrateur|Raphaël est venu.
+narrateur|Le toboggan a gardé sa feuille.
+enfant-f|J'ai écouté. Puis j'ai raconté.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+maman|On t'a écoutée.
+maman|Si malaise, tu reviens nous le dire.
+narrateur|Le gant rouge est presque sec.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr"/>
@@ -11223,7 +11948,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Noé va vers les balançoires. Le sol est un peu froid. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Noé se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On range un objet. Je suis là. On reste ensemble.</t>
+          <t>Nina va vers les balançoires. La chaîne fait tic, tout léger. Le siège est un peu humide. Elle a écouté la maîtresse. Le malaise est encore là, tout petit. Ce soir, je raconte. Oui. À la maison. Donne-moi ta main. La main de papa est tiède. On écoute la maîtresse. Si tu as un malaise, tu racontes. Raconter à la maison. C'est ça. Bravo, Nina. Une goutte tombe de la chaîne.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11363,11 +12088,27 @@
       <c r="AV60" s="2" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>narrateur|Noé va vers les balançoires. Le sol est un peu froid. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Noé se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On range un objet.
-maman|Je suis là. On reste ensemble.</t>
-        </is>
-      </c>
-      <c r="AX60" t="inlineStr"/>
+          <t>narrateur|Nina va vers les balançoires.
+narrateur|La chaîne fait tic, tout léger.
+narrateur|Le siège est un peu humide.
+narrateur|Elle a écouté la maîtresse.
+narrateur|Le malaise est encore là, tout petit.
+enfant-f|Ce soir, je raconte.
+maman|Oui. À la maison.
+papa|Donne-moi ta main.
+narrateur|La main de papa est tiède.
+maman|On écoute la maîtresse.
+maman|Si tu as un malaise, tu racontes.
+enfant-f|Raconter à la maison.
+papa|C'est ça. Bravo, Nina.
+narrateur|Une goutte tombe de la chaîne.</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>balancoire</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11392,7 +12133,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
+          <t>On écoute la maîtresse ?</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -11552,7 +12293,7 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
+          <t>narrateur|On écoute la maîtresse ?</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr"/>
@@ -11580,7 +12321,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé respire. Noé retient : écouter, si malaise raconter à la maison. On continue, avec maman.</t>
+          <t>Oui. On écoute la maîtresse. Si malaise, raconter à la maison. Nina hoche la tête. On continue, avec nous. D'accord, papa. Bravo, Nina.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -11724,7 +12465,13 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé respire. Noé retient : écouter, si malaise raconter à la maison. On continue, avec maman.</t>
+          <t>narrateur|Oui.
+maman|On écoute la maîtresse.
+maman|Si malaise, raconter à la maison.
+narrateur|Nina hoche la tête.
+papa|On continue, avec nous.
+enfant-f|D'accord, papa.
+maman|Bravo, Nina.</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr"/>
@@ -11752,7 +12499,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>Nina prend quoi ? Le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -11916,7 +12663,8 @@
       <c r="AV63" s="2" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>narrateur|Nina prend quoi ?
+papa|Le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr"/>
@@ -11944,7 +12692,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Noé a choisi le ballon. Un chat miaule une fois. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé répète tout bas : écouter, si malaise raconter à la maison. On dit merci. papa n'est pas loin.</t>
+          <t>Plus tard, Nina prend le ballon. Le ballon roule sous la balançoire. Elle est encore aux balançoires. J'ai écouté la maîtresse. J'ai un malaise. Tu as bien fait de raconter. Tu as écouté, à l'école. Si malaise, tu viens nous le dire. Je raconte à la maison. Bravo, Nina. C'est du bon travail. Le ballon est un peu froid. Je t'écoute. On reste un moment.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12084,10 +12832,26 @@
       <c r="AV64" s="2" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>narrateur|Noé a choisi le ballon. Un chat miaule une fois. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé répète tout bas : écouter, si malaise raconter à la maison. On dit merci. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX64" t="inlineStr"/>
+          <t>narrateur|Plus tard, Nina prend le ballon.
+narrateur|Le ballon roule sous la balançoire.
+narrateur|Elle est encore aux balançoires.
+enfant-f|J'ai écouté la maîtresse.
+enfant-f|J'ai un malaise.
+papa|Tu as bien fait de raconter.
+maman|Tu as écouté, à l'école.
+papa|Si malaise, tu viens nous le dire.
+enfant-f|Je raconte à la maison.
+maman|Bravo, Nina.
+maman|C'est du bon travail.
+narrateur|Le ballon est un peu froid.
+papa|Je t'écoute. On reste un moment.</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>ballon</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12112,7 +12876,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Qui arrive, au parc ? Nino, Mila, ou Raphaël.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12280,7 +13044,8 @@
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Qui arrive, au parc ?
+maman|Nino, Mila, ou Raphaël.</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr"/>
@@ -12308,7 +13073,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint Tom. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de les balançoires, le ballon et Tom. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
+          <t>Nino pousse la balançoire, tout doux. Le ballon attend dans l'herbe. Nina tient la chaîne. Nina est aux balançoires. Elle a le ballon. Bonjour, Nino. Bonjour, Nina. J'ai raconté mon malaise. Oui. Tu as écouté, puis raconté. Si malaise, raconter à la maison. Tu as parlé à maman ? Oui. Et à papa. On écoute la maîtresse. Puis on raconte, à la maison. Le ventre de Nina se desserre, tout doucement. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12448,10 +13213,29 @@
       <c r="AV66" s="2" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>narrateur|Noé rejoint Tom. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de les balançoires, le ballon et Tom. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX66" t="inlineStr"/>
+          <t>narrateur|Nino pousse la balançoire, tout doux.
+narrateur|Le ballon attend dans l'herbe.
+narrateur|Nina tient la chaîne.
+narrateur|Nina est aux balançoires.
+narrateur|Elle a le ballon.
+enfant-f|Bonjour, Nino.
+enfant-m|Bonjour, Nina.
+enfant-f|J'ai raconté mon malaise.
+papa|Oui. Tu as écouté, puis raconté.
+maman|Si malaise, raconter à la maison.
+enfant-m|Tu as parlé à maman ?
+enfant-f|Oui. Et à papa.
+papa|On écoute la maîtresse.
+maman|Puis on raconte, à la maison.
+narrateur|Le ventre de Nina se desserre, tout doucement.
+enfant-f|Merci, papa. Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12476,7 +13260,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué aux balançoires. Elle a pris le ballon. Nino est venu. La chaîne a fait tic, encore un peu. J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. On t'a écoutée. Si malaise, tu reviens nous le dire. Le gant rouge est presque sec. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -12616,7 +13400,17 @@
       <c r="AV67" s="2" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a joué aux balançoires.
+narrateur|Elle a pris le ballon.
+narrateur|Nino est venu.
+narrateur|La chaîne a fait tic, encore un peu.
+enfant-f|J'ai écouté. Puis j'ai raconté.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+maman|On t'a écoutée.
+maman|Si malaise, tu reviens nous le dire.
+narrateur|Le gant rouge est presque sec.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr"/>
@@ -12644,7 +13438,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint Léa. Un chat miaule une fois. On dit merci. Cette fin-là est celle de les balançoires, le ballon et Léa. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
+          <t>Mila s'assoit sur l'autre balançoire. Le ballon est entre les deux. Nina balance un peu, tout lentement. Nina est aux balançoires. Elle a le ballon. Bonjour, Mila. Bonjour, Nina. J'ai raconté mon malaise. Oui. Tu as écouté, puis raconté. Si malaise, raconter à la maison. Tu as parlé à maman ? Oui. Et à papa. On écoute la maîtresse. Puis on raconte, à la maison. Le ventre de Nina se desserre, tout doucement. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12784,10 +13578,29 @@
       <c r="AV68" s="2" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>narrateur|Noé rejoint Léa. Un chat miaule une fois. On dit merci. Cette fin-là est celle de les balançoires, le ballon et Léa. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX68" t="inlineStr"/>
+          <t>narrateur|Mila s'assoit sur l'autre balançoire.
+narrateur|Le ballon est entre les deux.
+narrateur|Nina balance un peu, tout lentement.
+narrateur|Nina est aux balançoires.
+narrateur|Elle a le ballon.
+enfant-f|Bonjour, Mila.
+enfant-f|Bonjour, Nina.
+enfant-f|J'ai raconté mon malaise.
+papa|Oui. Tu as écouté, puis raconté.
+maman|Si malaise, raconter à la maison.
+enfant-f|Tu as parlé à maman ?
+enfant-f|Oui. Et à papa.
+papa|On écoute la maîtresse.
+maman|Puis on raconte, à la maison.
+narrateur|Le ventre de Nina se desserre, tout doucement.
+enfant-f|Merci, papa. Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12812,7 +13625,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué aux balançoires. Elle a pris le ballon. Mila est venue. La chaîne a fait tic, encore un peu. J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. On t'a écoutée. Si malaise, tu reviens nous le dire. Le gant rouge est presque sec. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12952,7 +13765,17 @@
       <c r="AV69" s="2" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a joué aux balançoires.
+narrateur|Elle a pris le ballon.
+narrateur|Mila est venue.
+narrateur|La chaîne a fait tic, encore un peu.
+enfant-f|J'ai écouté. Puis j'ai raconté.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+maman|On t'a écoutée.
+maman|Si malaise, tu reviens nous le dire.
+narrateur|Le gant rouge est presque sec.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr"/>
@@ -12980,7 +13803,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint Sami. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de les balançoires, le ballon et Sami. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
+          <t>Raphaël ramasse le ballon sous la balançoire. Il le pose sur les genoux de Nina. La chaîne fait tic. Nina est aux balançoires. Elle a le ballon. Bonjour, Raphaël. Bonjour, Nina. J'ai raconté mon malaise. Oui. Tu as écouté, puis raconté. Si malaise, raconter à la maison. Tu as parlé à maman ? Oui. Et à papa. On écoute la maîtresse. Puis on raconte, à la maison. Le ventre de Nina se desserre, tout doucement. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -13120,10 +13943,29 @@
       <c r="AV70" s="2" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>narrateur|Noé rejoint Sami. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de les balançoires, le ballon et Sami. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX70" t="inlineStr"/>
+          <t>narrateur|Raphaël ramasse le ballon sous la balançoire.
+narrateur|Il le pose sur les genoux de Nina.
+narrateur|La chaîne fait tic.
+narrateur|Nina est aux balançoires.
+narrateur|Elle a le ballon.
+enfant-f|Bonjour, Raphaël.
+enfant-m|Bonjour, Nina.
+enfant-f|J'ai raconté mon malaise.
+papa|Oui. Tu as écouté, puis raconté.
+maman|Si malaise, raconter à la maison.
+enfant-m|Tu as parlé à maman ?
+enfant-f|Oui. Et à papa.
+papa|On écoute la maîtresse.
+maman|Puis on raconte, à la maison.
+narrateur|Le ventre de Nina se desserre, tout doucement.
+enfant-f|Merci, papa. Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13148,7 +13990,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué aux balançoires. Elle a pris le ballon. Raphaël est venu. La chaîne a fait tic, encore un peu. J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. On t'a écoutée. Si malaise, tu reviens nous le dire. Le gant rouge est presque sec. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -13288,7 +14130,17 @@
       <c r="AV71" s="2" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a joué aux balançoires.
+narrateur|Elle a pris le ballon.
+narrateur|Raphaël est venu.
+narrateur|La chaîne a fait tic, encore un peu.
+enfant-f|J'ai écouté. Puis j'ai raconté.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+maman|On t'a écoutée.
+maman|Si malaise, tu reviens nous le dire.
+narrateur|Le gant rouge est presque sec.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr"/>
@@ -13316,7 +14168,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Noé a choisi le seau. Les chaussures font toc toc. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé répète tout bas : écouter, si malaise raconter à la maison. On souffle doucement. papa n'est pas loin.</t>
+          <t>Plus tard, Nina prend le seau. Le seau pend près du gant. Elle pense encore aux balançoires. J'ai écouté la maîtresse. J'ai eu un malaise. Raconte. On est là. Un camarade a parlé tout bas. Tu as bien fait de le dire. À la maison. On écoute la maîtresse. Si malaise, raconter à papa ou maman. Bravo. Ton ventre peut se desserrer. Une goutte glisse du bord du seau. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -13456,10 +14308,27 @@
       <c r="AV72" s="2" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>narrateur|Noé a choisi le seau. Les chaussures font toc toc. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé répète tout bas : écouter, si malaise raconter à la maison. On souffle doucement. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX72" t="inlineStr"/>
+          <t>narrateur|Plus tard, Nina prend le seau.
+narrateur|Le seau pend près du gant.
+narrateur|Elle pense encore aux balançoires.
+enfant-f|J'ai écouté la maîtresse.
+enfant-f|J'ai eu un malaise.
+papa|Raconte. On est là.
+enfant-f|Un camarade a parlé tout bas.
+maman|Tu as bien fait de le dire.
+maman|À la maison.
+papa|On écoute la maîtresse.
+papa|Si malaise, raconter à papa ou maman.
+maman|Bravo. Ton ventre peut se desserrer.
+narrateur|Une goutte glisse du bord du seau.
+enfant-f|Merci, papa. Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>seau</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13484,7 +14353,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Qui arrive, au parc ? Nino, Mila, ou Raphaël.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -13652,7 +14521,8 @@
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Qui arrive, au parc ?
+maman|Nino, Mila, ou Raphaël.</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr"/>
@@ -13680,7 +14550,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint Tom. Un chat miaule une fois. On range un objet. Cette fin-là est celle de les balançoires, le seau et Tom. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
+          <t>Nino a le seau près des pieds. Nina balance, tout petit. Le seau ne bouge pas. Nina est aux balançoires. Elle a le seau. Bonjour, Nino. Bonjour, Nina. J'ai raconté mon malaise. Oui. Tu as écouté, puis raconté. Si malaise, raconter à la maison. Tu as parlé à maman ? Oui. Et à papa. On écoute la maîtresse. Puis on raconte, à la maison. Le ventre de Nina se desserre, tout doucement. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13820,10 +14690,29 @@
       <c r="AV74" s="2" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>narrateur|Noé rejoint Tom. Un chat miaule une fois. On range un objet. Cette fin-là est celle de les balançoires, le seau et Tom. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX74" t="inlineStr"/>
+          <t>narrateur|Nino a le seau près des pieds.
+narrateur|Nina balance, tout petit.
+narrateur|Le seau ne bouge pas.
+narrateur|Nina est aux balançoires.
+narrateur|Elle a le seau.
+enfant-f|Bonjour, Nino.
+enfant-m|Bonjour, Nina.
+enfant-f|J'ai raconté mon malaise.
+papa|Oui. Tu as écouté, puis raconté.
+maman|Si malaise, raconter à la maison.
+enfant-m|Tu as parlé à maman ?
+enfant-f|Oui. Et à papa.
+papa|On écoute la maîtresse.
+maman|Puis on raconte, à la maison.
+narrateur|Le ventre de Nina se desserre, tout doucement.
+enfant-f|Merci, papa. Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13848,7 +14737,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué aux balançoires. Elle a pris le seau. Nino est venu. La chaîne a fait tic, encore un peu. J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. On t'a écoutée. Si malaise, tu reviens nous le dire. Le gant rouge est presque sec. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -13988,7 +14877,17 @@
       <c r="AV75" s="2" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a joué aux balançoires.
+narrateur|Elle a pris le seau.
+narrateur|Nino est venu.
+narrateur|La chaîne a fait tic, encore un peu.
+enfant-f|J'ai écouté. Puis j'ai raconté.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+maman|On t'a écoutée.
+maman|Si malaise, tu reviens nous le dire.
+narrateur|Le gant rouge est presque sec.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr"/>
@@ -14016,7 +14915,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint Léa. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de les balançoires, le seau et Léa. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
+          <t>Mila met le seau sous la balançoire. Comme une maison, tout rouge. Nina rit. Nina est aux balançoires. Elle a le seau. Bonjour, Mila. Bonjour, Nina. J'ai raconté mon malaise. Oui. Tu as écouté, puis raconté. Si malaise, raconter à la maison. Tu as parlé à maman ? Oui. Et à papa. On écoute la maîtresse. Puis on raconte, à la maison. Le ventre de Nina se desserre, tout doucement. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14156,10 +15055,29 @@
       <c r="AV76" s="2" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>narrateur|Noé rejoint Léa. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de les balançoires, le seau et Léa. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX76" t="inlineStr"/>
+          <t>narrateur|Mila met le seau sous la balançoire.
+narrateur|Comme une maison, tout rouge.
+narrateur|Nina rit.
+narrateur|Nina est aux balançoires.
+narrateur|Elle a le seau.
+enfant-f|Bonjour, Mila.
+enfant-f|Bonjour, Nina.
+enfant-f|J'ai raconté mon malaise.
+papa|Oui. Tu as écouté, puis raconté.
+maman|Si malaise, raconter à la maison.
+enfant-f|Tu as parlé à maman ?
+enfant-f|Oui. Et à papa.
+papa|On écoute la maîtresse.
+maman|Puis on raconte, à la maison.
+narrateur|Le ventre de Nina se desserre, tout doucement.
+enfant-f|Merci, papa. Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14184,7 +15102,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué aux balançoires. Elle a pris le seau. Mila est venue. La chaîne a fait tic, encore un peu. J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. On t'a écoutée. Si malaise, tu reviens nous le dire. Le gant rouge est presque sec. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -14324,7 +15242,17 @@
       <c r="AV77" s="2" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a joué aux balançoires.
+narrateur|Elle a pris le seau.
+narrateur|Mila est venue.
+narrateur|La chaîne a fait tic, encore un peu.
+enfant-f|J'ai écouté. Puis j'ai raconté.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+maman|On t'a écoutée.
+maman|Si malaise, tu reviens nous le dire.
+narrateur|Le gant rouge est presque sec.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr"/>
@@ -14352,7 +15280,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint Sami. La couverture est douce. On souffle doucement. Cette fin-là est celle de les balançoires, le seau et Sami. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
+          <t>Raphaël verse de l'air dans le seau. Pour de faux, tout sérieux. Nina arrête la balançoire. Nina est aux balançoires. Elle a le seau. Bonjour, Raphaël. Bonjour, Nina. J'ai raconté mon malaise. Oui. Tu as écouté, puis raconté. Si malaise, raconter à la maison. Tu as parlé à maman ? Oui. Et à papa. On écoute la maîtresse. Puis on raconte, à la maison. Le ventre de Nina se desserre, tout doucement. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14492,10 +15420,29 @@
       <c r="AV78" s="2" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>narrateur|Noé rejoint Sami. La couverture est douce. On souffle doucement. Cette fin-là est celle de les balançoires, le seau et Sami. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX78" t="inlineStr"/>
+          <t>narrateur|Raphaël verse de l'air dans le seau.
+narrateur|Pour de faux, tout sérieux.
+narrateur|Nina arrête la balançoire.
+narrateur|Nina est aux balançoires.
+narrateur|Elle a le seau.
+enfant-f|Bonjour, Raphaël.
+enfant-m|Bonjour, Nina.
+enfant-f|J'ai raconté mon malaise.
+papa|Oui. Tu as écouté, puis raconté.
+maman|Si malaise, raconter à la maison.
+enfant-m|Tu as parlé à maman ?
+enfant-f|Oui. Et à papa.
+papa|On écoute la maîtresse.
+maman|Puis on raconte, à la maison.
+narrateur|Le ventre de Nina se desserre, tout doucement.
+enfant-f|Merci, papa. Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14520,7 +15467,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué aux balançoires. Elle a pris le seau. Raphaël est venu. La chaîne a fait tic, encore un peu. J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. On t'a écoutée. Si malaise, tu reviens nous le dire. Le gant rouge est presque sec. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -14660,7 +15607,17 @@
       <c r="AV79" s="2" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a joué aux balançoires.
+narrateur|Elle a pris le seau.
+narrateur|Raphaël est venu.
+narrateur|La chaîne a fait tic, encore un peu.
+enfant-f|J'ai écouté. Puis j'ai raconté.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+maman|On t'a écoutée.
+maman|Si malaise, tu reviens nous le dire.
+narrateur|Le gant rouge est presque sec.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr"/>
@@ -14688,7 +15645,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Noé a choisi le doudou. La couverture est douce. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé répète tout bas : écouter, si malaise raconter à la maison. On écoute jusqu'au bout. papa n'est pas loin.</t>
+          <t>Plus tard, Nina prend le doudou. Le doudou est coincé contre la chaîne. Nina pense encore aux balançoires. Papa s'assoit sur le banc. J'ai un malaise. Je raconte à la maison. On t'écoute. Un camarade a chuchoté, à l'école. Tu as écouté la maîtresse. Puis tu nous as dit. Si malaise, tu racontes à la maison. Bravo, Nina. Tu as fait du bon travail. Le doudou est doux, un peu froissé. Tu veux rester un peu ? Oui.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14828,10 +15785,28 @@
       <c r="AV80" s="2" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>narrateur|Noé a choisi le doudou. La couverture est douce. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé répète tout bas : écouter, si malaise raconter à la maison. On écoute jusqu'au bout. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX80" t="inlineStr"/>
+          <t>narrateur|Plus tard, Nina prend le doudou.
+narrateur|Le doudou est coincé contre la chaîne.
+narrateur|Nina pense encore aux balançoires.
+narrateur|Papa s'assoit sur le banc.
+enfant-f|J'ai un malaise.
+enfant-f|Je raconte à la maison.
+maman|On t'écoute.
+enfant-f|Un camarade a chuchoté, à l'école.
+papa|Tu as écouté la maîtresse.
+papa|Puis tu nous as dit.
+maman|Si malaise, tu racontes à la maison.
+papa|Bravo, Nina. Tu as fait du bon travail.
+narrateur|Le doudou est doux, un peu froissé.
+maman|Tu veux rester un peu ?
+enfant-f|Oui.</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>doudou</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14856,7 +15831,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Qui arrive, au parc ? Nino, Mila, ou Raphaël.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -15024,7 +15999,8 @@
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Qui arrive, au parc ?
+maman|Nino, Mila, ou Raphaël.</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr"/>
@@ -15052,7 +16028,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint Tom. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de les balançoires, le doudou et Tom. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
+          <t>Nino pose le doudou à côté. Le doudou voyage, tout doux. Nina le regarde. Nina est aux balançoires. Elle a le doudou. Bonjour, Nino. Bonjour, Nina. J'ai raconté mon malaise. Oui. Tu as écouté, puis raconté. Si malaise, raconter à la maison. Tu as parlé à maman ? Oui. Et à papa. On écoute la maîtresse. Puis on raconte, à la maison. Le ventre de Nina se desserre, tout doucement. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -15192,10 +16168,29 @@
       <c r="AV82" s="2" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>narrateur|Noé rejoint Tom. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de les balançoires, le doudou et Tom. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX82" t="inlineStr"/>
+          <t>narrateur|Nino pose le doudou à côté.
+narrateur|Le doudou voyage, tout doux.
+narrateur|Nina le regarde.
+narrateur|Nina est aux balançoires.
+narrateur|Elle a le doudou.
+enfant-f|Bonjour, Nino.
+enfant-m|Bonjour, Nina.
+enfant-f|J'ai raconté mon malaise.
+papa|Oui. Tu as écouté, puis raconté.
+maman|Si malaise, raconter à la maison.
+enfant-m|Tu as parlé à maman ?
+enfant-f|Oui. Et à papa.
+papa|On écoute la maîtresse.
+maman|Puis on raconte, à la maison.
+narrateur|Le ventre de Nina se desserre, tout doucement.
+enfant-f|Merci, papa. Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15220,7 +16215,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué aux balançoires. Elle a pris le doudou. Nino est venu. La chaîne a fait tic, encore un peu. J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. On t'a écoutée. Si malaise, tu reviens nous le dire. Le gant rouge est presque sec. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -15360,7 +16355,17 @@
       <c r="AV83" s="2" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a joué aux balançoires.
+narrateur|Elle a pris le doudou.
+narrateur|Nino est venu.
+narrateur|La chaîne a fait tic, encore un peu.
+enfant-f|J'ai écouté. Puis j'ai raconté.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+maman|On t'a écoutée.
+maman|Si malaise, tu reviens nous le dire.
+narrateur|Le gant rouge est presque sec.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr"/>
@@ -15388,7 +16393,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint Léa. La couverture est douce. On dit merci. Cette fin-là est celle de les balançoires, le doudou et Léa. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
+          <t>Mila cale le doudou contre Nina. Pour qu'il ne tombe pas. Nina le serre. Nina est aux balançoires. Elle a le doudou. Bonjour, Mila. Bonjour, Nina. J'ai raconté mon malaise. Oui. Tu as écouté, puis raconté. Si malaise, raconter à la maison. Tu as parlé à maman ? Oui. Et à papa. On écoute la maîtresse. Puis on raconte, à la maison. Le ventre de Nina se desserre, tout doucement. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -15528,10 +16533,29 @@
       <c r="AV84" s="2" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>narrateur|Noé rejoint Léa. La couverture est douce. On dit merci. Cette fin-là est celle de les balançoires, le doudou et Léa. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX84" t="inlineStr"/>
+          <t>narrateur|Mila cale le doudou contre Nina.
+narrateur|Pour qu'il ne tombe pas.
+narrateur|Nina le serre.
+narrateur|Nina est aux balançoires.
+narrateur|Elle a le doudou.
+enfant-f|Bonjour, Mila.
+enfant-f|Bonjour, Nina.
+enfant-f|J'ai raconté mon malaise.
+papa|Oui. Tu as écouté, puis raconté.
+maman|Si malaise, raconter à la maison.
+enfant-f|Tu as parlé à maman ?
+enfant-f|Oui. Et à papa.
+papa|On écoute la maîtresse.
+maman|Puis on raconte, à la maison.
+narrateur|Le ventre de Nina se desserre, tout doucement.
+enfant-f|Merci, papa. Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15556,7 +16580,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué aux balançoires. Elle a pris le doudou. Mila est venue. La chaîne a fait tic, encore un peu. J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. On t'a écoutée. Si malaise, tu reviens nous le dire. Le gant rouge est presque sec. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -15696,7 +16720,17 @@
       <c r="AV85" s="2" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a joué aux balançoires.
+narrateur|Elle a pris le doudou.
+narrateur|Mila est venue.
+narrateur|La chaîne a fait tic, encore un peu.
+enfant-f|J'ai écouté. Puis j'ai raconté.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+maman|On t'a écoutée.
+maman|Si malaise, tu reviens nous le dire.
+narrateur|Le gant rouge est presque sec.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr"/>
@@ -15724,7 +16758,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint Sami. On entend un oiseau. On souffle doucement. Cette fin-là est celle de les balançoires, le doudou et Sami. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
+          <t>Raphaël a mis le doudou sur le banc. Il voit le gant rouge, tout loin. Nina balance encore un peu. Nina est aux balançoires. Elle a le doudou. Bonjour, Raphaël. Bonjour, Nina. J'ai raconté mon malaise. Oui. Tu as écouté, puis raconté. Si malaise, raconter à la maison. Tu as parlé à maman ? Oui. Et à papa. On écoute la maîtresse. Puis on raconte, à la maison. Le ventre de Nina se desserre, tout doucement. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15864,10 +16898,29 @@
       <c r="AV86" s="2" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>narrateur|Noé rejoint Sami. On entend un oiseau. On souffle doucement. Cette fin-là est celle de les balançoires, le doudou et Sami. Noé a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Noé a entendu : écouter, si malaise raconter à la maison. Noé dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX86" t="inlineStr"/>
+          <t>narrateur|Raphaël a mis le doudou sur le banc.
+narrateur|Il voit le gant rouge, tout loin.
+narrateur|Nina balance encore un peu.
+narrateur|Nina est aux balançoires.
+narrateur|Elle a le doudou.
+enfant-f|Bonjour, Raphaël.
+enfant-m|Bonjour, Nina.
+enfant-f|J'ai raconté mon malaise.
+papa|Oui. Tu as écouté, puis raconté.
+maman|Si malaise, raconter à la maison.
+enfant-m|Tu as parlé à maman ?
+enfant-f|Oui. Et à papa.
+papa|On écoute la maîtresse.
+maman|Puis on raconte, à la maison.
+narrateur|Le ventre de Nina se desserre, tout doucement.
+enfant-f|Merci, papa. Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15892,7 +16945,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a joué aux balançoires. Elle a pris le doudou. Raphaël est venu. La chaîne a fait tic, encore un peu. J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. On t'a écoutée. Si malaise, tu reviens nous le dire. Le gant rouge est presque sec. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -16032,7 +17085,17 @@
       <c r="AV87" s="2" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a joué aux balançoires.
+narrateur|Elle a pris le doudou.
+narrateur|Raphaël est venu.
+narrateur|La chaîne a fait tic, encore un peu.
+enfant-f|J'ai écouté. Puis j'ai raconté.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+maman|On t'a écoutée.
+maman|Si malaise, tu reviens nous le dire.
+narrateur|Le gant rouge est presque sec.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr"/>
@@ -16054,7 +17117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16148,6 +17211,13 @@
       <c r="A13" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-COL-014.xlsx
+++ b/stories/arbres/TREE-COL-014.xlsx
@@ -3871,17 +3871,17 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Nina attrape le seau, toute seule. Elle verse l'eau sur le sable. Le trou se ferme. Le rouge disparaît. Oh. Le seau était à moi, une minute. Je voulais laver le gant. Nina pose le seau, déçue. Tu peux le prendre comment ? S'il te plaît, le seau. Oui. Pour creuser, pas noyer. Nina pousse le sable, cuillère après cuillère. Le pouce rouge revient, un peu propre.</t>
+          <t>Nina attrape le seau, toute seule. Elle verse l'eau sur le sable. Le trou se ferme. Le rouge disparaît. Oh. Le seau était à moi, une minute. Je voulais laver le gant. Nina pose le seau, déçue. Tu le prends avec moi ? S'il te plaît, le seau. Oui. Pour creuser, pas noyer. Nina pousse le sable, cuillère après cuillère. Le pouce rouge revient, un peu propre.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Nina attrape le seau, toute seule. Elle verse l'eau sur le sable. Le trou se ferme. Le rouge disparaît. Oh. Le seau était à moi, une minute. Je voulais laver le &lt;emphasis level="moderate"&gt;gant&lt;/emphasis&gt;. Nina pose le seau, déçue. Tu peux le prendre comment ? S'il te plaît, le seau. Oui. Pour creuser, pas noyer. Nina pousse le sable, cuillère après cuillère. Le pouce rouge revient, un peu propre.&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Nina attrape le seau, toute seule. Elle verse l'eau sur le sable. Le trou se ferme. Le rouge disparaît. Oh. Le seau était à moi, une minute. Je voulais laver le &lt;emphasis level="moderate"&gt;gant&lt;/emphasis&gt;. Nina pose le seau, déçue. Tu le prends avec moi ? S'il te plaît, le seau. Oui. Pour creuser, pas noyer. Nina pousse le sable, cuillère après cuillère. Le pouce rouge revient, un peu propre.&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;Nina attrape le seau, toute seule. Elle verse l'eau sur le sable. Le trou se ferme. Le rouge disparaît. Oh. Le seau était à moi, une minute. Je voulais laver le &lt;emphasis&gt;gant&lt;/emphasis&gt;. Nina pose le seau, déçue. Tu peux le prendre comment ? S'il te plaît, le seau. Oui. Pour creuser, pas noyer. Nina pousse le sable, cuillère après cuillère. Le pouce rouge revient, un peu propre.&lt;/low-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;Nina attrape le seau, toute seule. Elle verse l'eau sur le sable. Le trou se ferme. Le rouge disparaît. Oh. Le seau était à moi, une minute. Je voulais laver le &lt;emphasis&gt;gant&lt;/emphasis&gt;. Nina pose le seau, déçue. Tu le prends avec moi ? S'il te plaît, le seau. Oui. Pour creuser, pas noyer. Nina pousse le sable, cuillère après cuillère. Le pouce rouge revient, un peu propre.&lt;/low-pitch&gt; [pause]</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
@@ -4027,7 +4027,7 @@
 maman|Le seau était à moi, une minute.
 enfant-f|Je voulais laver le gant.
 narrateur|Nina pose le seau, déçue.
-papa|Tu peux le prendre comment ?
+papa|Tu le prends avec moi ?
 enfant-f|S'il te plaît, le seau.
 maman|Oui.
 maman|Pour creuser, pas noyer.
@@ -5382,17 +5382,17 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Nina prend le doudou sur le banc. Elle l'enroule autour du gant sableux. La laine du doudou se remplit de grains. Il est sale ! Ce doudou n'aime pas le sable. Je voulais le gant au chaud. Le doudou, tu le prends comment ? S'il te plaît, un coin. Un coin, oui. Pas tout le doudou. Nina frotte le gant avec le coin. Les grains tombent. Le rouge reparaît.</t>
+          <t>Nina prend le doudou sur le banc. Elle l'enroule autour du gant sableux. La laine du doudou se remplit de grains. Il est sale ! Ce doudou n'aime pas le sable. Je voulais le gant au chaud. Le doudou, tu le prends avec moi ? enfant-f|S'il te plaît, un coin. Un coin, oui. Pas tout le doudou. Nina frotte le gant avec le coin. Les grains tombent. Le rouge reparaît.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Nina prend le doudou sur le banc. Elle l'enroule autour du &lt;emphasis level="moderate"&gt;gant&lt;/emphasis&gt; sableux. La laine du doudou se remplit de grains. Il est sale ! Ce doudou n'aime pas le sable. Je voulais le gant au chaud. Le doudou, tu le prends comment ? S'il te plaît, un coin. Un coin, oui. Pas tout le doudou. Nina frotte le gant avec le coin. Les grains tombent. Le rouge reparaît.&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Nina prend le doudou sur le banc. Elle l'enroule autour du &lt;emphasis level="moderate"&gt;gant&lt;/emphasis&gt; sableux. La laine du doudou se remplit de grains. Il est sale ! Ce doudou n'aime pas le sable. Je voulais le gant au chaud. Le doudou, tu le prends avec moi ? enfant-f|S'il te plaît, un coin. Un coin, oui. Pas tout le doudou. Nina frotte le gant avec le coin. Les grains tombent. Le rouge reparaît.&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;Nina prend le doudou sur le banc. Elle l'enroule autour du &lt;emphasis&gt;gant&lt;/emphasis&gt; sableux. La laine du doudou se remplit de grains. Il est sale ! Ce doudou n'aime pas le sable. Je voulais le gant au chaud. Le doudou, tu le prends comment ? S'il te plaît, un coin. Un coin, oui. Pas tout le doudou. Nina frotte le gant avec le coin. Les grains tombent. Le rouge reparaît.&lt;/low-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;Nina prend le doudou sur le banc. Elle l'enroule autour du &lt;emphasis&gt;gant&lt;/emphasis&gt; sableux. La laine du doudou se remplit de grains. Il est sale ! Ce doudou n'aime pas le sable. Je voulais le gant au chaud. Le doudou, tu le prends avec moi ? enfant-f|S'il te plaît, un coin. Un coin, oui. Pas tout le doudou. Nina frotte le gant avec le coin. Les grains tombent. Le rouge reparaît.&lt;/low-pitch&gt; [pause]</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr"/>
@@ -5536,8 +5536,8 @@
 enfant-f|Il est sale !
 maman|Ce doudou n'aime pas le sable.
 enfant-f|Je voulais le gant au chaud.
-papa|Le doudou, tu le prends comment ?
-enfant-f|S'il te plaît, un coin.
+papa|Le doudou, tu le prends avec moi ?
+papa|enfant-f|S'il te plaît, un coin.
 maman|Un coin, oui.
 maman|Pas tout le doudou.
 narrateur|Nina frotte le gant avec le coin.
@@ -6887,17 +6887,17 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Nina grimpe le toboggan à l'envers. Le métal pique ses paumes nues. Le gant rouge a glissé en bas. Je l'attrape ! Son pied pousse le gant, par erreur. Le rouge part dans une flaque de boue. Non ! Maman essuie le cartable, plus loin. Elle n'a pas vu le geste. Ça va, Nina ? Le gant. La boue l'a pris. Nina serre les poings, trop petite. Le métal lui refroidit les genoux. J'arrive. Attends une seconde.</t>
+          <t>Nina grimpe le toboggan à l'envers. Le métal pique ses paumes nues. Le gant rouge a glissé en bas. Je l'attrape ! Son pied pousse le gant, par erreur. Le rouge part dans une flaque de boue. Non ! Maman essuie le cartable, plus loin. Elle n'a pas vu le pied. Ça va, Nina ? Le gant. La boue l'a pris. Nina serre les poings, trop petite. Le métal lui refroidit les genoux. J'arrive. Attends une seconde.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nina grimpe le toboggan à l'envers. Le métal pique ses paumes nues. Le &lt;emphasis level="moderate"&gt;gant rouge&lt;/emphasis&gt; a glissé en bas. Je l'attrape ! Son pied pousse le gant, par erreur. Le rouge part dans une flaque de boue. Non ! Maman essuie le cartable, plus loin. Elle n'a pas vu le geste. Ça va, Nina ? Le gant. La boue l'a pris. Nina serre les poings, trop petite. Le métal lui refroidit les genoux. J'arrive. Attends une seconde.&lt;/prosody&gt;&lt;break time="420ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nina grimpe le toboggan à l'envers. Le métal pique ses paumes nues. Le &lt;emphasis level="moderate"&gt;gant rouge&lt;/emphasis&gt; a glissé en bas. Je l'attrape ! Son pied pousse le gant, par erreur. Le rouge part dans une flaque de boue. Non ! Maman essuie le cartable, plus loin. Elle n'a pas vu le pied. Ça va, Nina ? Le gant. La boue l'a pris. Nina serre les poings, trop petite. Le métal lui refroidit les genoux. J'arrive. Attends une seconde.&lt;/prosody&gt;&lt;break time="420ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Nina grimpe le toboggan à l'envers. Le métal pique ses paumes nues. Le &lt;emphasis&gt;gant rouge&lt;/emphasis&gt; a glissé en bas. Je l'attrape ! Son pied pousse le gant, par erreur. Le rouge part dans une flaque de boue. Non ! Maman essuie le cartable, plus loin. Elle n'a pas vu le geste. Ça va, Nina ? Le gant. La boue l'a pris. Nina serre les poings, trop petite. Le métal lui refroidit les genoux. J'arrive. Attends une seconde. [pause]</t>
+          <t>Nina grimpe le toboggan à l'envers. Le métal pique ses paumes nues. Le &lt;emphasis&gt;gant rouge&lt;/emphasis&gt; a glissé en bas. Je l'attrape ! Son pied pousse le gant, par erreur. Le rouge part dans une flaque de boue. Non ! Maman essuie le cartable, plus loin. Elle n'a pas vu le pied. Ça va, Nina ? Le gant. La boue l'a pris. Nina serre les poings, trop petite. Le métal lui refroidit les genoux. J'arrive. Attends une seconde. [pause]</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr"/>
@@ -7039,7 +7039,7 @@
 narrateur|Le rouge part dans une flaque de boue.
 enfant-f|Non !
 narrateur|Maman essuie le cartable, plus loin.
-narrateur|Elle n'a pas vu le geste.
+narrateur|Elle n'a pas vu le pied.
 maman|Ça va, Nina ?
 enfant-f|Le gant.
 enfant-f|La boue l'a pris.
@@ -7639,17 +7639,17 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Nina lance le ballon vers la boue. Le ballon tape le gant, puis s'enfonce. Les deux sont pris ! Le ballon n'était pas à toi, Nina. Je voulais pousser le gant. Nina avance, les pieds qui glissent. Tu peux demander, avant de lancer ? S'il te plaît, le ballon. On le sort ensemble, alors. Papa tire le ballon. Le gant bouge. Un lacet rouge se décolle de la boue.</t>
+          <t>Nina lance le ballon vers la boue. Le ballon tape le gant, puis s'enfonce. Les deux sont pris ! Le ballon n'était pas à toi, Nina. Je voulais pousser le gant. Nina avance, les pieds qui glissent. Le ballon, tu le lances où ? S'il te plaît, le ballon. On le sort ensemble, alors. Papa tire le ballon. Le gant bouge. Un lacet rouge se décolle de la boue.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Nina lance le ballon vers la boue. Le ballon tape le &lt;emphasis level="moderate"&gt;gant&lt;/emphasis&gt;, puis s'enfonce. Les deux sont pris ! Le ballon n'était pas à toi, Nina. Je voulais pousser le gant. Nina avance, les pieds qui glissent. Tu peux demander, avant de lancer ? S'il te plaît, le ballon. On le sort ensemble, alors. Papa tire le ballon. Le gant bouge. Un lacet rouge se décolle de la boue.&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Nina lance le ballon vers la boue. Le ballon tape le &lt;emphasis level="moderate"&gt;gant&lt;/emphasis&gt;, puis s'enfonce. Les deux sont pris ! Le ballon n'était pas à toi, Nina. Je voulais pousser le gant. Nina avance, les pieds qui glissent. Le ballon, tu le lances où ? S'il te plaît, le ballon. On le sort ensemble, alors. Papa tire le ballon. Le gant bouge. Un lacet rouge se décolle de la boue.&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;Nina lance le ballon vers la boue. Le ballon tape le &lt;emphasis&gt;gant&lt;/emphasis&gt;, puis s'enfonce. Les deux sont pris ! Le ballon n'était pas à toi, Nina. Je voulais pousser le gant. Nina avance, les pieds qui glissent. Tu peux demander, avant de lancer ? S'il te plaît, le ballon. On le sort ensemble, alors. Papa tire le ballon. Le gant bouge. Un lacet rouge se décolle de la boue.&lt;/low-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;Nina lance le ballon vers la boue. Le ballon tape le &lt;emphasis&gt;gant&lt;/emphasis&gt;, puis s'enfonce. Les deux sont pris ! Le ballon n'était pas à toi, Nina. Je voulais pousser le gant. Nina avance, les pieds qui glissent. Le ballon, tu le lances où ? S'il te plaît, le ballon. On le sort ensemble, alors. Papa tire le ballon. Le gant bouge. Un lacet rouge se décolle de la boue.&lt;/low-pitch&gt; [pause]</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr"/>
@@ -7793,7 +7793,7 @@
 papa|Le ballon n'était pas à toi, Nina.
 enfant-f|Je voulais pousser le gant.
 narrateur|Nina avance, les pieds qui glissent.
-maman|Tu peux demander, avant de lancer ?
+maman|Le ballon, tu le lances où ?
 enfant-f|S'il te plaît, le ballon.
 papa|On le sort ensemble, alors.
 narrateur|Papa tire le ballon.
@@ -9142,17 +9142,17 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Nina emporte le seau jusqu'au toboggan. Elle verse. L'eau et la boue se mêlent. Le gant nage, plus loin, plus sale. Reviens ! Ce seau servait à rincer les bottes. Je voulais laver le rouge. On verse où, si on demande ? S'il te plaît, un peu d'eau. Un filet, pas tout le seau. Nina penche, tout doucement. La boue s'ouvre. Le gant reste.</t>
+          <t>Nina emporte le seau jusqu'au toboggan. Elle verse. L'eau et la boue se mêlent. Le gant nage, plus loin, plus sale. Reviens ! Ce seau servait à rincer les bottes. Je voulais laver le rouge. On verse où, cette fois ? S'il te plaît, un peu d'eau. Un filet, pas tout le seau. Nina penche, tout doucement. La boue s'ouvre. Le gant reste.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Nina emporte le seau jusqu'au toboggan. Elle verse. L'eau et la boue se mêlent. Le &lt;emphasis level="moderate"&gt;gant&lt;/emphasis&gt; nage, plus loin, plus sale. Reviens ! Ce seau servait à rincer les bottes. Je voulais laver le rouge. On verse où, si on demande ? S'il te plaît, un peu d'eau. Un filet, pas tout le seau. Nina penche, tout doucement. La boue s'ouvre. Le gant reste.&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Nina emporte le seau jusqu'au toboggan. Elle verse. L'eau et la boue se mêlent. Le &lt;emphasis level="moderate"&gt;gant&lt;/emphasis&gt; nage, plus loin, plus sale. Reviens ! Ce seau servait à rincer les bottes. Je voulais laver le rouge. On verse où, cette fois ? S'il te plaît, un peu d'eau. Un filet, pas tout le seau. Nina penche, tout doucement. La boue s'ouvre. Le gant reste.&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;Nina emporte le seau jusqu'au toboggan. Elle verse. L'eau et la boue se mêlent. Le &lt;emphasis&gt;gant&lt;/emphasis&gt; nage, plus loin, plus sale. Reviens ! Ce seau servait à rincer les bottes. Je voulais laver le rouge. On verse où, si on demande ? S'il te plaît, un peu d'eau. Un filet, pas tout le seau. Nina penche, tout doucement. La boue s'ouvre. Le gant reste.&lt;/low-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;Nina emporte le seau jusqu'au toboggan. Elle verse. L'eau et la boue se mêlent. Le &lt;emphasis&gt;gant&lt;/emphasis&gt; nage, plus loin, plus sale. Reviens ! Ce seau servait à rincer les bottes. Je voulais laver le rouge. On verse où, cette fois ? S'il te plaît, un peu d'eau. Un filet, pas tout le seau. Nina penche, tout doucement. La boue s'ouvre. Le gant reste.&lt;/low-pitch&gt; [pause]</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr"/>
@@ -9297,7 +9297,7 @@
 enfant-f|Reviens !
 maman|Ce seau servait à rincer les bottes.
 enfant-f|Je voulais laver le rouge.
-papa|On verse où, si on demande ?
+papa|On verse où, cette fois ?
 enfant-f|S'il te plaît, un peu d'eau.
 maman|Un filet, pas tout le seau.
 narrateur|Nina penche, tout doucement.
@@ -10654,17 +10654,17 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Nina glisse le doudou sur le métal. Elle veut attraper le gant, de loin. Le doudou glisse, trop vite, dans la boue. Non, doudou ! Il n'était pas un filet, ce doudou. J'avais froid aux mains. Tu le prends comment, la prochaine ? S'il te plaît, le doudou. On le tient à deux, alors. Nina tient une oreille. Papa l'autre. Le doudou touche le gant, sans tomber.</t>
+          <t>Nina glisse le doudou sur le métal. Elle veut attraper le gant, de loin. Le doudou glisse, trop vite, dans la boue. Non, doudou ! Il n'était pas un filet, ce doudou. J'avais froid aux mains. Tu le prends avec moi, alors ? S'il te plaît, le doudou. On le tient à deux, alors. Nina tient une oreille. Papa l'autre. Le doudou touche le gant, sans tomber.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Nina glisse le doudou sur le métal. Elle veut attraper le &lt;emphasis level="moderate"&gt;gant&lt;/emphasis&gt;, de loin. Le doudou glisse, trop vite, dans la boue. Non, doudou ! Il n'était pas un filet, ce doudou. J'avais froid aux mains. Tu le prends comment, la prochaine ? S'il te plaît, le doudou. On le tient à deux, alors. Nina tient une oreille. Papa l'autre. Le doudou touche le gant, sans tomber.&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Nina glisse le doudou sur le métal. Elle veut attraper le &lt;emphasis level="moderate"&gt;gant&lt;/emphasis&gt;, de loin. Le doudou glisse, trop vite, dans la boue. Non, doudou ! Il n'était pas un filet, ce doudou. J'avais froid aux mains. Tu le prends avec moi, alors ? S'il te plaît, le doudou. On le tient à deux, alors. Nina tient une oreille. Papa l'autre. Le doudou touche le gant, sans tomber.&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;Nina glisse le doudou sur le métal. Elle veut attraper le &lt;emphasis&gt;gant&lt;/emphasis&gt;, de loin. Le doudou glisse, trop vite, dans la boue. Non, doudou ! Il n'était pas un filet, ce doudou. J'avais froid aux mains. Tu le prends comment, la prochaine ? S'il te plaît, le doudou. On le tient à deux, alors. Nina tient une oreille. Papa l'autre. Le doudou touche le gant, sans tomber.&lt;/low-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;Nina glisse le doudou sur le métal. Elle veut attraper le &lt;emphasis&gt;gant&lt;/emphasis&gt;, de loin. Le doudou glisse, trop vite, dans la boue. Non, doudou ! Il n'était pas un filet, ce doudou. J'avais froid aux mains. Tu le prends avec moi, alors ? S'il te plaît, le doudou. On le tient à deux, alors. Nina tient une oreille. Papa l'autre. Le doudou touche le gant, sans tomber.&lt;/low-pitch&gt; [pause]</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr"/>
@@ -10808,7 +10808,7 @@
 enfant-f|Non, doudou !
 papa|Il n'était pas un filet, ce doudou.
 enfant-f|J'avais froid aux mains.
-maman|Tu le prends comment, la prochaine ?
+maman|Tu le prends avec moi, alors ?
 enfant-f|S'il te plaît, le doudou.
 papa|On le tient à deux, alors.
 narrateur|Nina tient une oreille.
@@ -11045,17 +11045,17 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Nino pose le doudou en haut du toboggan. Il veut le faire glisser, comme un luge. Non, il va dans la boue ! C'est drôle ! S'il te plaît, Nino. On le tient. On ne le lance pas. On le tient. Ils tiennent les deux oreilles. Le doudou touche le gant. Papa le saisit. Vous l'avez gardé, au lieu de le jeter.</t>
+          <t>Nino pose le doudou en haut du toboggan. Il veut le faire glisser, comme une luge. Non, il va dans la boue ! C'est drôle ! S'il te plaît, Nino. On le tient. On ne le lance pas. On le tient. Ils tiennent les deux oreilles. Le doudou touche le gant. Papa le saisit. Vous l'avez gardé, au lieu de le jeter.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nino pose le doudou en haut du toboggan. Il veut le faire glisser, comme un luge. Non, il va dans la boue ! C'est drôle ! S'il te plaît, Nino. On le tient. On ne le lance pas. On le tient. Ils tiennent les deux oreilles. Le doudou touche le &lt;emphasis level="moderate"&gt;gant&lt;/emphasis&gt;. Papa le saisit. Vous l'avez gardé, au lieu de le jeter.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nino pose le doudou en haut du toboggan. Il veut le faire glisser, comme une luge. Non, il va dans la boue ! C'est drôle ! S'il te plaît, Nino. On le tient. On ne le lance pas. On le tient. Ils tiennent les deux oreilles. Le doudou touche le &lt;emphasis level="moderate"&gt;gant&lt;/emphasis&gt;. Papa le saisit. Vous l'avez gardé, au lieu de le jeter.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Nino pose le doudou en haut du toboggan. Il veut le faire glisser, comme un luge. Non, il va dans la boue ! C'est drôle ! S'il te plaît, Nino. On le tient. On ne le lance pas. On le tient. Ils tiennent les deux oreilles. Le doudou touche le &lt;emphasis&gt;gant&lt;/emphasis&gt;. Papa le saisit. Vous l'avez gardé, au lieu de le jeter. [pause]</t>
+          <t>Nino pose le doudou en haut du toboggan. Il veut le faire glisser, comme une luge. Non, il va dans la boue ! C'est drôle ! S'il te plaît, Nino. On le tient. On ne le lance pas. On le tient. Ils tiennent les deux oreilles. Le doudou touche le &lt;emphasis&gt;gant&lt;/emphasis&gt;. Papa le saisit. Vous l'avez gardé, au lieu de le jeter. [pause]</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr"/>
@@ -11190,7 +11190,7 @@
       <c r="AW54" t="inlineStr">
         <is>
           <t>narrateur|Nino pose le doudou en haut du toboggan.
-narrateur|Il veut le faire glisser, comme un luge.
+narrateur|Il veut le faire glisser, comme une luge.
 enfant-f|Non, il va dans la boue !
 enfant-m|C'est drôle !
 enfant-f|S'il te plaît, Nino.
@@ -13310,17 +13310,17 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Nino vise le gant avec le ballon. Nina lève les deux mains. Pas trop fort ! Je touche le rouge ! S'il te plaît, Nino. Tout près, pas un coup. Tout près. Nino pose le ballon contre le barreau. Le gant bascule dans les mains de papa. Le coup est devenu un geste. Merci, Nino.</t>
+          <t>Nino vise le gant avec le ballon. Nina lève les deux mains. Pas trop fort ! Je touche le rouge ! S'il te plaît, Nino. Tout près, pas un coup. Tout près. Nino pose le ballon contre le barreau. Le gant bascule dans les mains de papa. Le ballon a poussé, sans frapper. Merci, Nino.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nino vise le &lt;emphasis level="moderate"&gt;gant&lt;/emphasis&gt; avec le ballon. Nina lève les deux mains. Pas trop fort ! Je touche le rouge ! S'il te plaît, Nino. Tout près, pas un coup. Tout près. Nino pose le ballon contre le barreau. Le gant bascule dans les mains de papa. Le coup est devenu un geste. Merci, Nino.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nino vise le &lt;emphasis level="moderate"&gt;gant&lt;/emphasis&gt; avec le ballon. Nina lève les deux mains. Pas trop fort ! Je touche le rouge ! S'il te plaît, Nino. Tout près, pas un coup. Tout près. Nino pose le ballon contre le barreau. Le gant bascule dans les mains de papa. Le ballon a poussé, sans frapper. Merci, Nino.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Nino vise le &lt;emphasis&gt;gant&lt;/emphasis&gt; avec le ballon. Nina lève les deux mains. Pas trop fort ! Je touche le rouge ! S'il te plaît, Nino. Tout près, pas un coup. Tout près. Nino pose le ballon contre le barreau. Le gant bascule dans les mains de papa. Le coup est devenu un geste. Merci, Nino. [pause]</t>
+          <t>Nino vise le &lt;emphasis&gt;gant&lt;/emphasis&gt; avec le ballon. Nina lève les deux mains. Pas trop fort ! Je touche le rouge ! S'il te plaît, Nino. Tout près, pas un coup. Tout près. Nino pose le ballon contre le barreau. Le gant bascule dans les mains de papa. Le ballon a poussé, sans frapper. Merci, Nino. [pause]</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr"/>
@@ -13463,7 +13463,7 @@
 enfant-m|Tout près.
 narrateur|Nino pose le ballon contre le barreau.
 narrateur|Le gant bascule dans les mains de papa.
-maman|Le coup est devenu un geste.
+maman|Le ballon a poussé, sans frapper.
 enfant-f|Merci, Nino.</t>
         </is>
       </c>
@@ -14428,17 +14428,17 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Nina pose le seau sous la barrière. Elle monte dessus, sans rien dire. Le seau bascule. Nina recule. Ça bouge ! Ce seau n'est pas un tabouret. Le gant est trop haut. Tu veux de l'aide, comment ? S'il te plaît, tu me portes ? Oui. Les pieds au sol, d'abord. Nina attend. Papa s'accroupit. Le seau reste vide, à sa place.</t>
+          <t>Nina pose le seau sous la barrière. Elle monte dessus, sans rien dire. Le seau bascule. Nina recule. Ça bouge ! Ce seau n'est pas un tabouret. Le gant est trop haut. Tu veux que je t'aide ? S'il te plaît, tu me portes ? Oui. Les pieds au sol, d'abord. Nina attend. Papa s'accroupit. Le seau reste vide, à sa place.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Nina pose le seau sous la barrière. Elle monte dessus, sans rien dire. Le seau bascule. Nina recule. Ça bouge ! Ce seau n'est pas un tabouret. Le &lt;emphasis level="moderate"&gt;gant&lt;/emphasis&gt; est trop haut. Tu veux de l'aide, comment ? S'il te plaît, tu me portes ? Oui. Les pieds au sol, d'abord. Nina attend. Papa s'accroupit. Le seau reste vide, à sa place.&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Nina pose le seau sous la barrière. Elle monte dessus, sans rien dire. Le seau bascule. Nina recule. Ça bouge ! Ce seau n'est pas un tabouret. Le &lt;emphasis level="moderate"&gt;gant&lt;/emphasis&gt; est trop haut. Tu veux que je t'aide ? S'il te plaît, tu me portes ? Oui. Les pieds au sol, d'abord. Nina attend. Papa s'accroupit. Le seau reste vide, à sa place.&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;Nina pose le seau sous la barrière. Elle monte dessus, sans rien dire. Le seau bascule. Nina recule. Ça bouge ! Ce seau n'est pas un tabouret. Le &lt;emphasis&gt;gant&lt;/emphasis&gt; est trop haut. Tu veux de l'aide, comment ? S'il te plaît, tu me portes ? Oui. Les pieds au sol, d'abord. Nina attend. Papa s'accroupit. Le seau reste vide, à sa place.&lt;/low-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;Nina pose le seau sous la barrière. Elle monte dessus, sans rien dire. Le seau bascule. Nina recule. Ça bouge ! Ce seau n'est pas un tabouret. Le &lt;emphasis&gt;gant&lt;/emphasis&gt; est trop haut. Tu veux que je t'aide ? S'il te plaît, tu me portes ? Oui. Les pieds au sol, d'abord. Nina attend. Papa s'accroupit. Le seau reste vide, à sa place.&lt;/low-pitch&gt; [pause]</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr"/>
@@ -14583,7 +14583,7 @@
 enfant-f|Ça bouge !
 maman|Ce seau n'est pas un tabouret.
 enfant-f|Le gant est trop haut.
-papa|Tu veux de l'aide, comment ?
+papa|Tu veux que je t'aide ?
 enfant-f|S'il te plaît, tu me portes ?
 maman|Oui.
 maman|Les pieds au sol, d'abord.
@@ -14821,17 +14821,17 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Nino monte sur le seau, à son tour. Le seau penche. Nina recule. Ça va tomber ! Je touche ! S'il te plaît, Nino. Pieds par terre. Papa nous porte. Pieds par terre. Nino descend. Papa s'accroupit. Nina demande, bas, le dernier geste. S'il te plaît, tu l'attrapes ? Voilà. Le gant quitte le barreau, dans sa main.</t>
+          <t>Nino monte sur le seau, à son tour. Le seau penche. Nina recule. Ça va tomber ! Je touche ! S'il te plaît, Nino. Pieds par terre. Papa nous porte. Pieds par terre. Nino descend. Papa s'accroupit. Nina parle, bas, une dernière fois. S'il te plaît, tu l'attrapes ? Voilà. Le gant quitte le barreau, dans sa main.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nino monte sur le seau, à son tour. Le seau penche. Nina recule. Ça va tomber ! Je touche ! S'il te plaît, Nino. Pieds par terre. Papa nous porte. Pieds par terre. Nino descend. Papa s'accroupit. Nina demande, bas, le dernier geste. S'il te plaît, tu l'attrapes ? Voilà. Le &lt;emphasis level="moderate"&gt;gant&lt;/emphasis&gt; quitte le barreau, dans sa main.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nino monte sur le seau, à son tour. Le seau penche. Nina recule. Ça va tomber ! Je touche ! S'il te plaît, Nino. Pieds par terre. Papa nous porte. Pieds par terre. Nino descend. Papa s'accroupit. Nina parle, bas, une dernière fois. S'il te plaît, tu l'attrapes ? Voilà. Le &lt;emphasis level="moderate"&gt;gant&lt;/emphasis&gt; quitte le barreau, dans sa main.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Nino monte sur le seau, à son tour. Le seau penche. Nina recule. Ça va tomber ! Je touche ! S'il te plaît, Nino. Pieds par terre. Papa nous porte. Pieds par terre. Nino descend. Papa s'accroupit. Nina demande, bas, le dernier geste. S'il te plaît, tu l'attrapes ? Voilà. Le &lt;emphasis&gt;gant&lt;/emphasis&gt; quitte le barreau, dans sa main. [pause]</t>
+          <t>Nino monte sur le seau, à son tour. Le seau penche. Nina recule. Ça va tomber ! Je touche ! S'il te plaît, Nino. Pieds par terre. Papa nous porte. Pieds par terre. Nino descend. Papa s'accroupit. Nina parle, bas, une dernière fois. S'il te plaît, tu l'attrapes ? Voilà. Le &lt;emphasis&gt;gant&lt;/emphasis&gt; quitte le barreau, dans sa main. [pause]</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr"/>
@@ -14976,7 +14976,7 @@
 enfant-m|Pieds par terre.
 narrateur|Nino descend.
 narrateur|Papa s'accroupit.
-narrateur|Nina demande, bas, le dernier geste.
+narrateur|Nina parle, bas, une dernière fois.
 enfant-f|S'il te plaît, tu l'attrapes ?
 papa|Voilà.
 narrateur|Le gant quitte le barreau, dans sa main.</t>
@@ -15571,17 +15571,17 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Raphaël regarde l'eau du seau, comme un miroir. Le gant, là-haut ! Je vois le ciel ! Nina attend qu'il lève les yeux. S'il te plaît, Raphaël. Le seau reste. On demande à papa. D'accord. Ils posent le seau. Papa écoute. S'il te plaît, tu le décroches ? Oui. Le gant descend, un barreau à la fois.</t>
+          <t>Raphaël regarde l'eau du seau, comme un miroir. Le gant, là-haut ! Je vois le ciel ! Nina attend qu'il lève les yeux. S'il te plaît, Raphaël. Le seau reste. On appelle papa. D'accord. Ils posent le seau. Papa écoute. S'il te plaît, tu le décroches ? Oui. Le gant descend, un barreau à la fois.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Raphaël regarde l'eau du seau, comme un miroir. Le &lt;emphasis level="moderate"&gt;gant&lt;/emphasis&gt;, là-haut ! Je vois le ciel ! Nina attend qu'il lève les yeux. S'il te plaît, Raphaël. Le seau reste. On demande à papa. D'accord. Ils posent le seau. Papa écoute. S'il te plaît, tu le décroches ? Oui. Le gant descend, un barreau à la fois.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Raphaël regarde l'eau du seau, comme un miroir. Le &lt;emphasis level="moderate"&gt;gant&lt;/emphasis&gt;, là-haut ! Je vois le ciel ! Nina attend qu'il lève les yeux. S'il te plaît, Raphaël. Le seau reste. On appelle papa. D'accord. Ils posent le seau. Papa écoute. S'il te plaît, tu le décroches ? Oui. Le gant descend, un barreau à la fois.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Raphaël regarde l'eau du seau, comme un miroir. Le &lt;emphasis&gt;gant&lt;/emphasis&gt;, là-haut ! Je vois le ciel ! Nina attend qu'il lève les yeux. S'il te plaît, Raphaël. Le seau reste. On demande à papa. D'accord. Ils posent le seau. Papa écoute. S'il te plaît, tu le décroches ? Oui. Le gant descend, un barreau à la fois. [pause]</t>
+          <t>Raphaël regarde l'eau du seau, comme un miroir. Le &lt;emphasis&gt;gant&lt;/emphasis&gt;, là-haut ! Je vois le ciel ! Nina attend qu'il lève les yeux. S'il te plaît, Raphaël. Le seau reste. On appelle papa. D'accord. Ils posent le seau. Papa écoute. S'il te plaît, tu le décroches ? Oui. Le gant descend, un barreau à la fois. [pause]</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr"/>
@@ -15721,7 +15721,7 @@
 narrateur|Nina attend qu'il lève les yeux.
 enfant-f|S'il te plaît, Raphaël.
 enfant-f|Le seau reste.
-enfant-f|On demande à papa.
+enfant-f|On appelle papa.
 enfant-m|D'accord.
 narrateur|Ils posent le seau.
 narrateur|Papa écoute.
@@ -15945,17 +15945,17 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Nina jette le doudou vers le barreau. Le doudou s'accroche, à côté du gant. Les deux sont coincés ! Le doudou n'était pas un crochet. Je voulais tirer le rouge. On le décroche comment, alors ? S'il te plaît, tu l'attrapes ? Le doudou d'abord. Puis le gant. Nina attend, les bras le long du corps. Papa décroche l'oreille en peluche. Le gant penche, presque libre.</t>
+          <t>Nina jette le doudou vers le barreau. Le doudou s'accroche, à côté du gant. Les deux sont coincés ! Le doudou n'était pas un crochet. Je voulais tirer le rouge. On le décroche à deux, alors ? enfant-f|S'il te plaît, tu l'attrapes ? Le doudou d'abord. Puis le gant. Nina attend, les bras le long du corps. Papa décroche l'oreille en peluche. Le gant penche, presque libre.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Nina jette le doudou vers le barreau. Le doudou s'accroche, à côté du &lt;emphasis level="moderate"&gt;gant&lt;/emphasis&gt;. Les deux sont coincés ! Le doudou n'était pas un crochet. Je voulais tirer le rouge. On le décroche comment, alors ? S'il te plaît, tu l'attrapes ? Le doudou d'abord. Puis le gant. Nina attend, les bras le long du corps. Papa décroche l'oreille en peluche. Le gant penche, presque libre.&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Nina jette le doudou vers le barreau. Le doudou s'accroche, à côté du &lt;emphasis level="moderate"&gt;gant&lt;/emphasis&gt;. Les deux sont coincés ! Le doudou n'était pas un crochet. Je voulais tirer le rouge. On le décroche à deux, alors ? enfant-f|S'il te plaît, tu l'attrapes ? Le doudou d'abord. Puis le gant. Nina attend, les bras le long du corps. Papa décroche l'oreille en peluche. Le gant penche, presque libre.&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;Nina jette le doudou vers le barreau. Le doudou s'accroche, à côté du &lt;emphasis&gt;gant&lt;/emphasis&gt;. Les deux sont coincés ! Le doudou n'était pas un crochet. Je voulais tirer le rouge. On le décroche comment, alors ? S'il te plaît, tu l'attrapes ? Le doudou d'abord. Puis le gant. Nina attend, les bras le long du corps. Papa décroche l'oreille en peluche. Le gant penche, presque libre.&lt;/low-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;Nina jette le doudou vers le barreau. Le doudou s'accroche, à côté du &lt;emphasis&gt;gant&lt;/emphasis&gt;. Les deux sont coincés ! Le doudou n'était pas un crochet. Je voulais tirer le rouge. On le décroche à deux, alors ? enfant-f|S'il te plaît, tu l'attrapes ? Le doudou d'abord. Puis le gant. Nina attend, les bras le long du corps. Papa décroche l'oreille en peluche. Le gant penche, presque libre.&lt;/low-pitch&gt; [pause]</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr"/>
@@ -16098,8 +16098,8 @@
 enfant-f|Les deux sont coincés !
 papa|Le doudou n'était pas un crochet.
 enfant-f|Je voulais tirer le rouge.
-maman|On le décroche comment, alors ?
-enfant-f|S'il te plaît, tu l'attrapes ?
+maman|On le décroche à deux, alors ?
+maman|enfant-f|S'il te plaît, tu l'attrapes ?
 papa|Le doudou d'abord.
 papa|Puis le gant.
 narrateur|Nina attend, les bras le long du corps.
@@ -17451,7 +17451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -17564,6 +17564,13 @@
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
